--- a/reports/V116_202606.xlsx
+++ b/reports/V116_202606.xlsx
@@ -607,10 +607,10 @@
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
     <col width="9" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
   </cols>
@@ -638,7 +638,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>$12,000.00</t>
+          <t>$1,000.00</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-25 14:01:00</t>
+          <t>2026-06-25 15:23:00</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>$13,503.84</t>
+          <t>$1,666.06</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>$1,503.84</t>
+          <t>$666.06</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>$1,491.63</t>
+          <t>$661.44</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>$12.21</t>
+          <t>$4.62</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>+12.53%</t>
+          <t>+66.61%</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>-8.24%</t>
+          <t>-29.74%</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>14 / 9</t>
+          <t>15 / 9</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>60.87%</t>
+          <t>62.50%</t>
         </is>
       </c>
     </row>
@@ -934,11 +934,11 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>39.3%</t>
         </is>
       </c>
     </row>
@@ -949,11 +949,11 @@
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>27.9%</t>
         </is>
       </c>
     </row>
@@ -994,11 +994,11 @@
         </is>
       </c>
       <c r="B36" s="8" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>3.6%</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>154</v>
+        <v>160</v>
       </c>
     </row>
     <row r="41">
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="42">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="44">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1:0.34</t>
+          <t>1:0.29</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1:1.56</t>
+          <t>1:1.63</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
         <v>35</v>
       </c>
       <c r="D50" s="7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E50" s="7" t="n">
         <v>9</v>
@@ -1196,28 +1196,28 @@
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="H50" s="9" t="n">
-        <v>1491.630000000037</v>
+        <v>661.4400000000151</v>
       </c>
       <c r="I50" s="9" t="n">
-        <v>12.21</v>
+        <v>4.620000000000001</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>4.07</v>
+        <v>1.54</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>1503.840000000038</v>
+        <v>666.0600000000151</v>
       </c>
       <c r="L50" s="11" t="inlineStr">
         <is>
-          <t>+12.53%</t>
+          <t>+66.61%</t>
         </is>
       </c>
       <c r="M50" s="12" t="n">
-        <v>13503.84000000003</v>
+        <v>1666.060000000015</v>
       </c>
     </row>
   </sheetData>
@@ -1256,7 +1256,7 @@
     <col width="8" customWidth="1" min="12" max="12"/>
     <col width="21" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="21" customWidth="1" min="15" max="15"/>
     <col width="21" customWidth="1" min="16" max="16"/>
     <col width="9" customWidth="1" min="17" max="17"/>
     <col width="20" customWidth="1" min="18" max="18"/>
@@ -1404,28 +1404,28 @@
         </is>
       </c>
       <c r="M2" s="15" t="n">
-        <v>-407.6999999999825</v>
+        <v>-107.5099999999929</v>
       </c>
       <c r="N2" s="16" t="n">
-        <v>4.949999999999999</v>
+        <v>1.89</v>
       </c>
       <c r="O2" s="17" t="n">
-        <v>1.65</v>
+        <v>0.63</v>
       </c>
       <c r="P2" s="15" t="n">
-        <v>-402.7499999999825</v>
+        <v>-105.6199999999929</v>
       </c>
       <c r="Q2" s="18" t="inlineStr">
         <is>
-          <t>-3.36%</t>
+          <t>-10.56%</t>
         </is>
       </c>
       <c r="R2" s="19" t="n">
-        <v>11597.25000000001</v>
+        <v>894.3800000000072</v>
       </c>
       <c r="S2" s="18" t="inlineStr">
         <is>
-          <t>-3.36%</t>
+          <t>-10.56%</t>
         </is>
       </c>
     </row>
@@ -1473,24 +1473,24 @@
         </is>
       </c>
       <c r="M3" s="9" t="n">
-        <v>1567.860000000023</v>
+        <v>573.2000000000089</v>
       </c>
       <c r="N3" s="9" t="n">
-        <v>4.02</v>
+        <v>1.5</v>
       </c>
       <c r="O3" s="10" t="n">
-        <v>1.34</v>
+        <v>0.5</v>
       </c>
       <c r="P3" s="9" t="n">
-        <v>1571.880000000023</v>
+        <v>574.7000000000089</v>
       </c>
       <c r="Q3" s="11" t="inlineStr">
         <is>
-          <t>+13.55%</t>
+          <t>+64.26%</t>
         </is>
       </c>
       <c r="R3" s="12" t="n">
-        <v>13169.13000000004</v>
+        <v>1469.080000000016</v>
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
@@ -1542,28 +1542,28 @@
         </is>
       </c>
       <c r="M4" s="15" t="n">
-        <v>-475.5900000000006</v>
+        <v>-158.5800000000004</v>
       </c>
       <c r="N4" s="16" t="n">
-        <v>1.62</v>
+        <v>0.54</v>
       </c>
       <c r="O4" s="17" t="n">
-        <v>0.54</v>
+        <v>0.18</v>
       </c>
       <c r="P4" s="15" t="n">
-        <v>-473.9700000000005</v>
+        <v>-158.0400000000004</v>
       </c>
       <c r="Q4" s="18" t="inlineStr">
         <is>
-          <t>-3.60%</t>
+          <t>-10.76%</t>
         </is>
       </c>
       <c r="R4" s="19" t="n">
-        <v>12695.16000000004</v>
+        <v>1311.040000000016</v>
       </c>
       <c r="S4" s="18" t="inlineStr">
         <is>
-          <t>-3.60%</t>
+          <t>-10.76%</t>
         </is>
       </c>
     </row>
@@ -1577,16 +1577,16 @@
         <v>7</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>21</v>
@@ -1595,7 +1595,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J5" s="7" t="n">
         <v>56</v>
@@ -1607,28 +1607,28 @@
       </c>
       <c r="L5" s="21" t="inlineStr">
         <is>
-          <t>1:1.28</t>
+          <t>1:0.81</t>
         </is>
       </c>
       <c r="M5" s="9" t="n">
-        <v>807.0599999999972</v>
+        <v>354.3299999999995</v>
       </c>
       <c r="N5" s="9" t="n">
-        <v>1.62</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="O5" s="10" t="n">
-        <v>0.54</v>
+        <v>0.23</v>
       </c>
       <c r="P5" s="9" t="n">
-        <v>808.6799999999973</v>
+        <v>355.0199999999995</v>
       </c>
       <c r="Q5" s="11" t="inlineStr">
         <is>
-          <t>+6.37%</t>
+          <t>+27.08%</t>
         </is>
       </c>
       <c r="R5" s="12" t="n">
-        <v>13503.84000000003</v>
+        <v>1666.060000000015</v>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>4135.1</v>
       </c>
       <c r="P3" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>4134.171428571429</v>
       </c>
       <c r="P4" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q4" s="5" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>4133.242857142857</v>
       </c>
       <c r="P5" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q5" s="5" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>4132.314285714286</v>
       </c>
       <c r="P6" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q6" s="5" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>4131.385714285715</v>
       </c>
       <c r="P7" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q7" s="5" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>4130.457142857143</v>
       </c>
       <c r="P8" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q8" s="5" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>4129.528571428572</v>
       </c>
       <c r="P9" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q9" s="5" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>4128.6</v>
       </c>
       <c r="P10" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q10" s="5" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>4196.75</v>
       </c>
       <c r="P11" s="17" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q11" s="6" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>4196.75</v>
       </c>
       <c r="U11" s="15" t="n">
-        <v>-25.5</v>
+        <v>-12.75</v>
       </c>
       <c r="V11" s="13" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>4197.75</v>
       </c>
       <c r="P12" s="17" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q12" s="6" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>4197.75</v>
       </c>
       <c r="U12" s="15" t="n">
-        <v>-25.10000000000037</v>
+        <v>-12.55000000000018</v>
       </c>
       <c r="V12" s="13" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
         <v>4198.75</v>
       </c>
       <c r="P13" s="17" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q13" s="6" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>4198.75</v>
       </c>
       <c r="U13" s="15" t="n">
-        <v>-25.45999999999913</v>
+        <v>-12.72999999999956</v>
       </c>
       <c r="V13" s="13" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>4199.75</v>
       </c>
       <c r="P14" s="17" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q14" s="6" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>4199.75</v>
       </c>
       <c r="U14" s="15" t="n">
-        <v>-25.44000000000051</v>
+        <v>-12.72000000000026</v>
       </c>
       <c r="V14" s="13" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>4200.75</v>
       </c>
       <c r="P15" s="17" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q15" s="6" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>4200.75</v>
       </c>
       <c r="U15" s="15" t="n">
-        <v>-25.5</v>
+        <v>-12.75</v>
       </c>
       <c r="V15" s="13" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>4201.75</v>
       </c>
       <c r="P16" s="17" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q16" s="6" t="inlineStr">
         <is>
@@ -2991,7 +2991,7 @@
         <v>4201.75</v>
       </c>
       <c r="U16" s="15" t="n">
-        <v>-25.45999999999913</v>
+        <v>-12.72999999999956</v>
       </c>
       <c r="V16" s="13" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>4202.75</v>
       </c>
       <c r="P17" s="17" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q17" s="6" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>4202.75</v>
       </c>
       <c r="U17" s="15" t="n">
-        <v>-25.5</v>
+        <v>-12.75</v>
       </c>
       <c r="V17" s="13" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>4203.75</v>
       </c>
       <c r="P18" s="17" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q18" s="6" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>4203.75</v>
       </c>
       <c r="U18" s="15" t="n">
-        <v>-25.39999999999963</v>
+        <v>-12.69999999999982</v>
       </c>
       <c r="V18" s="13" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>4183.1</v>
       </c>
       <c r="P19" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q19" s="7" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>4213</v>
       </c>
       <c r="U19" s="9" t="n">
-        <v>54.39000000000033</v>
+        <v>18.13000000000011</v>
       </c>
       <c r="V19" s="20" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>4182.171428571429</v>
       </c>
       <c r="P20" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q20" s="7" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>4213</v>
       </c>
       <c r="U20" s="9" t="n">
-        <v>56.88000000000011</v>
+        <v>18.96000000000004</v>
       </c>
       <c r="V20" s="20" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>4181.242857142857</v>
       </c>
       <c r="P21" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q21" s="7" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>4213</v>
       </c>
       <c r="U21" s="9" t="n">
-        <v>59.64000000000033</v>
+        <v>19.88000000000011</v>
       </c>
       <c r="V21" s="20" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>4180.314285714286</v>
       </c>
       <c r="P22" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q22" s="7" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>4213</v>
       </c>
       <c r="U22" s="9" t="n">
-        <v>62.67000000000098</v>
+        <v>20.89000000000033</v>
       </c>
       <c r="V22" s="20" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>4179.385714285715</v>
       </c>
       <c r="P23" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q23" s="7" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>4213</v>
       </c>
       <c r="U23" s="9" t="n">
-        <v>65.88000000000011</v>
+        <v>21.96000000000004</v>
       </c>
       <c r="V23" s="20" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>4178.457142857143</v>
       </c>
       <c r="P24" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q24" s="7" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>4213</v>
       </c>
       <c r="U24" s="9" t="n">
-        <v>67.97999999999956</v>
+        <v>22.65999999999985</v>
       </c>
       <c r="V24" s="20" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>4177.528571428572</v>
       </c>
       <c r="P25" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q25" s="7" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>4213</v>
       </c>
       <c r="U25" s="9" t="n">
-        <v>70.85999999999967</v>
+        <v>23.61999999999989</v>
       </c>
       <c r="V25" s="20" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>4176.6</v>
       </c>
       <c r="P26" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q26" s="5" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>4230.75</v>
       </c>
       <c r="P27" s="34" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q27" s="5" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>4231.75</v>
       </c>
       <c r="P28" s="34" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q28" s="5" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>4232.75</v>
       </c>
       <c r="P29" s="34" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q29" s="5" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>4233.75</v>
       </c>
       <c r="P30" s="34" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q30" s="5" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>4234.75</v>
       </c>
       <c r="P31" s="34" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q31" s="5" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>4235.75</v>
       </c>
       <c r="P32" s="34" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q32" s="5" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         <v>4236.75</v>
       </c>
       <c r="P33" s="34" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q33" s="5" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         <v>4237.75</v>
       </c>
       <c r="P34" s="34" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q34" s="5" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>4173.1</v>
       </c>
       <c r="P35" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q35" s="5" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>4172.171428571429</v>
       </c>
       <c r="P36" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q36" s="5" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>4171.242857142857</v>
       </c>
       <c r="P37" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q37" s="5" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         <v>4170.314285714286</v>
       </c>
       <c r="P38" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q38" s="5" t="inlineStr">
         <is>
@@ -4901,7 +4901,7 @@
         <v>4169.385714285715</v>
       </c>
       <c r="P39" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q39" s="5" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
         <v>4168.457142857143</v>
       </c>
       <c r="P40" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q40" s="5" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>4167.528571428572</v>
       </c>
       <c r="P41" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q41" s="5" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
         <v>4166.6</v>
       </c>
       <c r="P42" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q42" s="5" t="inlineStr">
         <is>
@@ -5209,7 +5209,7 @@
         <v>4191.1</v>
       </c>
       <c r="P43" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q43" s="6" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>4191.1</v>
       </c>
       <c r="U43" s="15" t="n">
-        <v>-35.60999999999967</v>
+        <v>-11.86999999999989</v>
       </c>
       <c r="V43" s="13" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
         <v>4190.171428571429</v>
       </c>
       <c r="P44" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q44" s="6" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>4190.17</v>
       </c>
       <c r="U44" s="15" t="n">
-        <v>-35.57999999999902</v>
+        <v>-11.85999999999967</v>
       </c>
       <c r="V44" s="13" t="inlineStr">
         <is>
@@ -5389,13 +5389,13 @@
         <v>4221</v>
       </c>
       <c r="N45" s="38" t="n">
-        <v>4201.07</v>
+        <v>4201.08</v>
       </c>
       <c r="O45" s="38" t="n">
         <v>4189.242857142857</v>
       </c>
       <c r="P45" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q45" s="6" t="inlineStr">
         <is>
@@ -5416,7 +5416,7 @@
         <v>4189.24</v>
       </c>
       <c r="U45" s="15" t="n">
-        <v>-35.48999999999978</v>
+        <v>-11.84000000000015</v>
       </c>
       <c r="V45" s="13" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>4188.314285714286</v>
       </c>
       <c r="P46" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q46" s="6" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>4188.31</v>
       </c>
       <c r="U46" s="15" t="n">
-        <v>-35.25</v>
+        <v>-11.75</v>
       </c>
       <c r="V46" s="13" t="inlineStr">
         <is>
@@ -5575,13 +5575,13 @@
         <v>4221</v>
       </c>
       <c r="N47" s="38" t="n">
-        <v>4199.12</v>
+        <v>4199.19</v>
       </c>
       <c r="O47" s="38" t="n">
         <v>4187.385714285715</v>
       </c>
       <c r="P47" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q47" s="6" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>4187.39</v>
       </c>
       <c r="U47" s="15" t="n">
-        <v>-35.18999999999869</v>
+        <v>-11.79999999999927</v>
       </c>
       <c r="V47" s="13" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>4186.457142857143</v>
       </c>
       <c r="P48" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q48" s="6" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>4186.46</v>
       </c>
       <c r="U48" s="15" t="n">
-        <v>-35.6999999999989</v>
+        <v>-11.89999999999964</v>
       </c>
       <c r="V48" s="13" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         <v>4185.528571428572</v>
       </c>
       <c r="P49" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q49" s="6" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>4185.53</v>
       </c>
       <c r="U49" s="15" t="n">
-        <v>-35.67000000000098</v>
+        <v>-11.89000000000033</v>
       </c>
       <c r="V49" s="13" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>4184.6</v>
       </c>
       <c r="P50" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q50" s="6" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         <v>4184.6</v>
       </c>
       <c r="U50" s="15" t="n">
-        <v>-35.54999999999836</v>
+        <v>-11.84999999999945</v>
       </c>
       <c r="V50" s="13" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
         <v>4176.4</v>
       </c>
       <c r="P51" s="10" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q51" s="7" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>4208</v>
       </c>
       <c r="U51" s="9" t="n">
-        <v>36.13999999999942</v>
+        <v>18.06999999999971</v>
       </c>
       <c r="V51" s="20" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>4175.328571428571</v>
       </c>
       <c r="P52" s="10" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q52" s="7" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>4208</v>
       </c>
       <c r="U52" s="9" t="n">
-        <v>38.15999999999985</v>
+        <v>19.07999999999993</v>
       </c>
       <c r="V52" s="20" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>4174.257142857143</v>
       </c>
       <c r="P53" s="10" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q53" s="7" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         <v>4208</v>
       </c>
       <c r="U53" s="9" t="n">
-        <v>40.47999999999956</v>
+        <v>20.23999999999978</v>
       </c>
       <c r="V53" s="20" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>4173.185714285714</v>
       </c>
       <c r="P54" s="10" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q54" s="7" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         <v>4208</v>
       </c>
       <c r="U54" s="9" t="n">
-        <v>42.47999999999956</v>
+        <v>21.23999999999978</v>
       </c>
       <c r="V54" s="20" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>4172.114285714285</v>
       </c>
       <c r="P55" s="10" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q55" s="7" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>4208</v>
       </c>
       <c r="U55" s="9" t="n">
-        <v>44.60000000000036</v>
+        <v>22.30000000000018</v>
       </c>
       <c r="V55" s="20" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         <v>4171.042857142857</v>
       </c>
       <c r="P56" s="10" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q56" s="7" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>4208</v>
       </c>
       <c r="U56" s="9" t="n">
-        <v>46.73999999999978</v>
+        <v>23.36999999999989</v>
       </c>
       <c r="V56" s="20" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>4169.971428571428</v>
       </c>
       <c r="P57" s="10" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q57" s="7" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>4208</v>
       </c>
       <c r="U57" s="9" t="n">
-        <v>48.89999999999964</v>
+        <v>24.44999999999982</v>
       </c>
       <c r="V57" s="20" t="inlineStr">
         <is>
@@ -6598,13 +6598,13 @@
         <v>4208</v>
       </c>
       <c r="N58" s="40" t="n">
-        <v>4182.35</v>
+        <v>4182.48</v>
       </c>
       <c r="O58" s="40" t="n">
         <v>4168.9</v>
       </c>
       <c r="P58" s="41" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q58" s="8" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         <v>4177.71</v>
       </c>
       <c r="U58" s="42" t="n">
-        <v>-9.280000000000655</v>
+        <v>-4.769999999999527</v>
       </c>
       <c r="V58" s="43" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
       </c>
       <c r="W58" s="44" t="inlineStr">
         <is>
-          <t>-0.3R</t>
+          <t>-0.4R</t>
         </is>
       </c>
     </row>
@@ -6697,7 +6697,7 @@
         <v>4207.75</v>
       </c>
       <c r="P59" s="17" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q59" s="6" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         <v>4207.75</v>
       </c>
       <c r="U59" s="15" t="n">
-        <v>-25.13999999999942</v>
+        <v>-12.56999999999971</v>
       </c>
       <c r="V59" s="13" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>4208.75</v>
       </c>
       <c r="P60" s="17" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q60" s="6" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>4208.75</v>
       </c>
       <c r="U60" s="15" t="n">
-        <v>-25.45999999999913</v>
+        <v>-12.72999999999956</v>
       </c>
       <c r="V60" s="13" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>4209.75</v>
       </c>
       <c r="P61" s="17" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q61" s="6" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>4209.75</v>
       </c>
       <c r="U61" s="15" t="n">
-        <v>-25.45999999999913</v>
+        <v>-12.72999999999956</v>
       </c>
       <c r="V61" s="13" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         <v>4210.75</v>
       </c>
       <c r="P62" s="17" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q62" s="6" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
         <v>4210.75</v>
       </c>
       <c r="U62" s="15" t="n">
-        <v>-25.5</v>
+        <v>-12.75</v>
       </c>
       <c r="V62" s="13" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         <v>4211.75</v>
       </c>
       <c r="P63" s="10" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q63" s="7" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         <v>4177</v>
       </c>
       <c r="U63" s="9" t="n">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="V63" s="20" t="inlineStr">
         <is>
@@ -7162,7 +7162,7 @@
         <v>4212.75</v>
       </c>
       <c r="P64" s="10" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q64" s="7" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>4177</v>
       </c>
       <c r="U64" s="9" t="n">
-        <v>46.1200000000008</v>
+        <v>23.0600000000004</v>
       </c>
       <c r="V64" s="20" t="inlineStr">
         <is>
@@ -7255,7 +7255,7 @@
         <v>4213.75</v>
       </c>
       <c r="P65" s="10" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q65" s="7" t="inlineStr">
         <is>
@@ -7276,7 +7276,7 @@
         <v>4177</v>
       </c>
       <c r="U65" s="9" t="n">
-        <v>48.04000000000087</v>
+        <v>24.02000000000044</v>
       </c>
       <c r="V65" s="20" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         <v>4214.75</v>
       </c>
       <c r="P66" s="10" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q66" s="7" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         <v>4177</v>
       </c>
       <c r="U66" s="9" t="n">
-        <v>50.13999999999942</v>
+        <v>25.06999999999971</v>
       </c>
       <c r="V66" s="20" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>4181.1</v>
       </c>
       <c r="P67" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q67" s="6" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         <v>4181.1</v>
       </c>
       <c r="U67" s="15" t="n">
-        <v>-35.60999999999967</v>
+        <v>-11.86999999999989</v>
       </c>
       <c r="V67" s="13" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>4180.171428571429</v>
       </c>
       <c r="P68" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q68" s="6" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>4180.17</v>
       </c>
       <c r="U68" s="15" t="n">
-        <v>-35.6999999999989</v>
+        <v>-11.89999999999964</v>
       </c>
       <c r="V68" s="13" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>4179.242857142857</v>
       </c>
       <c r="P69" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q69" s="6" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>4179.24</v>
       </c>
       <c r="U69" s="15" t="n">
-        <v>-35.25</v>
+        <v>-11.75</v>
       </c>
       <c r="V69" s="13" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>4178.314285714286</v>
       </c>
       <c r="P70" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q70" s="6" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>4178.31</v>
       </c>
       <c r="U70" s="15" t="n">
-        <v>-35.09999999999945</v>
+        <v>-11.69999999999982</v>
       </c>
       <c r="V70" s="13" t="inlineStr">
         <is>
@@ -7813,7 +7813,7 @@
         <v>4177.385714285715</v>
       </c>
       <c r="P71" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q71" s="6" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>4177.39</v>
       </c>
       <c r="U71" s="15" t="n">
-        <v>-35.57999999999902</v>
+        <v>-11.85999999999967</v>
       </c>
       <c r="V71" s="13" t="inlineStr">
         <is>
@@ -7906,7 +7906,7 @@
         <v>4176.457142857143</v>
       </c>
       <c r="P72" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q72" s="6" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         <v>4176.46</v>
       </c>
       <c r="U72" s="15" t="n">
-        <v>-35.09999999999945</v>
+        <v>-11.69999999999982</v>
       </c>
       <c r="V72" s="13" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>4175.528571428572</v>
       </c>
       <c r="P73" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q73" s="6" t="inlineStr">
         <is>
@@ -8020,7 +8020,7 @@
         <v>4175.53</v>
       </c>
       <c r="U73" s="15" t="n">
-        <v>-35.70000000000164</v>
+        <v>-11.90000000000055</v>
       </c>
       <c r="V73" s="13" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>4174.6</v>
       </c>
       <c r="P74" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q74" s="6" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>4174.6</v>
       </c>
       <c r="U74" s="15" t="n">
-        <v>-35.66999999999825</v>
+        <v>-11.88999999999942</v>
       </c>
       <c r="V74" s="13" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>4185.1</v>
       </c>
       <c r="P75" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q75" s="6" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>4185.1</v>
       </c>
       <c r="U75" s="15" t="n">
-        <v>-35.27999999999793</v>
+        <v>-11.75999999999931</v>
       </c>
       <c r="V75" s="13" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>4184.171428571429</v>
       </c>
       <c r="P76" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q76" s="6" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         <v>4184.17</v>
       </c>
       <c r="U76" s="15" t="n">
-        <v>-35.60999999999967</v>
+        <v>-11.86999999999989</v>
       </c>
       <c r="V76" s="13" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>4183.242857142857</v>
       </c>
       <c r="P77" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q77" s="6" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>4183.24</v>
       </c>
       <c r="U77" s="15" t="n">
-        <v>-35.40000000000055</v>
+        <v>-11.80000000000018</v>
       </c>
       <c r="V77" s="13" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>4182.314285714286</v>
       </c>
       <c r="P78" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q78" s="6" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>4182.31</v>
       </c>
       <c r="U78" s="15" t="n">
-        <v>-35.39999999999782</v>
+        <v>-11.79999999999927</v>
       </c>
       <c r="V78" s="13" t="inlineStr">
         <is>
@@ -8557,7 +8557,7 @@
         <v>4181.385714285715</v>
       </c>
       <c r="P79" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q79" s="6" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>4181.39</v>
       </c>
       <c r="U79" s="15" t="n">
-        <v>-35.66999999999825</v>
+        <v>-11.88999999999942</v>
       </c>
       <c r="V79" s="13" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>4180.457142857143</v>
       </c>
       <c r="P80" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q80" s="6" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
         <v>4180.46</v>
       </c>
       <c r="U80" s="15" t="n">
-        <v>-35.60999999999967</v>
+        <v>-11.86999999999989</v>
       </c>
       <c r="V80" s="13" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
         <v>4179.528571428572</v>
       </c>
       <c r="P81" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q81" s="6" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>4179.53</v>
       </c>
       <c r="U81" s="15" t="n">
-        <v>-35.70000000000164</v>
+        <v>-11.90000000000055</v>
       </c>
       <c r="V81" s="13" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         <v>4178.6</v>
       </c>
       <c r="P82" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q82" s="6" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         <v>4178.6</v>
       </c>
       <c r="U82" s="15" t="n">
-        <v>-35.66999999999825</v>
+        <v>-11.88999999999942</v>
       </c>
       <c r="V82" s="13" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>4175.1</v>
       </c>
       <c r="P83" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q83" s="7" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>4205</v>
       </c>
       <c r="U83" s="9" t="n">
-        <v>54.11999999999989</v>
+        <v>18.03999999999996</v>
       </c>
       <c r="V83" s="20" t="inlineStr">
         <is>
@@ -9022,7 +9022,7 @@
         <v>4174.171428571429</v>
       </c>
       <c r="P84" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q84" s="6" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>4174.17</v>
       </c>
       <c r="U84" s="15" t="n">
-        <v>-35.6999999999989</v>
+        <v>-11.89999999999964</v>
       </c>
       <c r="V84" s="13" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>4173.242857142857</v>
       </c>
       <c r="P85" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q85" s="6" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
         <v>4173.24</v>
       </c>
       <c r="U85" s="15" t="n">
-        <v>-35.58000000000175</v>
+        <v>-11.86000000000058</v>
       </c>
       <c r="V85" s="13" t="inlineStr">
         <is>
@@ -9208,7 +9208,7 @@
         <v>4172.314285714286</v>
       </c>
       <c r="P86" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q86" s="6" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         <v>4172.31</v>
       </c>
       <c r="U86" s="15" t="n">
-        <v>-35.6399999999976</v>
+        <v>-11.8799999999992</v>
       </c>
       <c r="V86" s="13" t="inlineStr">
         <is>
@@ -9301,7 +9301,7 @@
         <v>4171.385714285715</v>
       </c>
       <c r="P87" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q87" s="6" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>4171.39</v>
       </c>
       <c r="U87" s="15" t="n">
-        <v>-35.6999999999989</v>
+        <v>-11.89999999999964</v>
       </c>
       <c r="V87" s="13" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
         <v>4170.457142857143</v>
       </c>
       <c r="P88" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q88" s="6" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         <v>4170.46</v>
       </c>
       <c r="U88" s="15" t="n">
-        <v>-35.67000000000098</v>
+        <v>-11.89000000000033</v>
       </c>
       <c r="V88" s="13" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>4169.528571428572</v>
       </c>
       <c r="P89" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q89" s="6" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         <v>4169.53</v>
       </c>
       <c r="U89" s="15" t="n">
-        <v>-35.28000000000065</v>
+        <v>-11.76000000000022</v>
       </c>
       <c r="V89" s="13" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>4168.6</v>
       </c>
       <c r="P90" s="41" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q90" s="8" t="inlineStr">
         <is>
@@ -9601,7 +9601,7 @@
         <v>4178.41</v>
       </c>
       <c r="U90" s="42" t="n">
-        <v>-6.06000000000131</v>
+        <v>-2.020000000000437</v>
       </c>
       <c r="V90" s="43" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>4155.75</v>
       </c>
       <c r="P91" s="34" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q91" s="5" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>4156.75</v>
       </c>
       <c r="P92" s="34" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q92" s="5" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>4157.75</v>
       </c>
       <c r="P93" s="34" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q93" s="5" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>4158.75</v>
       </c>
       <c r="P94" s="34" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q94" s="5" t="inlineStr">
         <is>
@@ -9981,7 +9981,7 @@
         <v>4159.75</v>
       </c>
       <c r="P95" s="34" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q95" s="5" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>4160.75</v>
       </c>
       <c r="P96" s="34" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q96" s="5" t="inlineStr">
         <is>
@@ -10135,7 +10135,7 @@
         <v>4161.75</v>
       </c>
       <c r="P97" s="34" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q97" s="5" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>4162.75</v>
       </c>
       <c r="P98" s="34" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q98" s="5" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>4137.75</v>
       </c>
       <c r="P99" s="34" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q99" s="5" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>4138.75</v>
       </c>
       <c r="P100" s="34" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q100" s="5" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>4139.75</v>
       </c>
       <c r="P101" s="34" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q101" s="5" t="inlineStr">
         <is>
@@ -10520,7 +10520,7 @@
         <v>4140.75</v>
       </c>
       <c r="P102" s="34" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q102" s="5" t="inlineStr">
         <is>
@@ -10597,7 +10597,7 @@
         <v>4141.75</v>
       </c>
       <c r="P103" s="34" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q103" s="5" t="inlineStr">
         <is>
@@ -10674,7 +10674,7 @@
         <v>4142.75</v>
       </c>
       <c r="P104" s="34" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q104" s="5" t="inlineStr">
         <is>
@@ -10751,7 +10751,7 @@
         <v>4143.75</v>
       </c>
       <c r="P105" s="34" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q105" s="5" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
         <v>4144.75</v>
       </c>
       <c r="P106" s="34" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q106" s="5" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         <v>4101.1</v>
       </c>
       <c r="P107" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q107" s="6" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         <v>4101.1</v>
       </c>
       <c r="U107" s="15" t="n">
-        <v>-35.6399999999976</v>
+        <v>-11.8799999999992</v>
       </c>
       <c r="V107" s="13" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         <v>4100.171428571429</v>
       </c>
       <c r="P108" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q108" s="6" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>4100.17</v>
       </c>
       <c r="U108" s="15" t="n">
-        <v>-35.57999999999902</v>
+        <v>-11.85999999999967</v>
       </c>
       <c r="V108" s="13" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>4099.242857142857</v>
       </c>
       <c r="P109" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q109" s="6" t="inlineStr">
         <is>
@@ -11112,7 +11112,7 @@
         <v>4099.24</v>
       </c>
       <c r="U109" s="15" t="n">
-        <v>-35.46000000000186</v>
+        <v>-11.82000000000062</v>
       </c>
       <c r="V109" s="13" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>4098.314285714286</v>
       </c>
       <c r="P110" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q110" s="6" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>4098.31</v>
       </c>
       <c r="U110" s="15" t="n">
-        <v>-35.66999999999825</v>
+        <v>-11.88999999999942</v>
       </c>
       <c r="V110" s="13" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>4097.385714285715</v>
       </c>
       <c r="P111" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q111" s="6" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
         <v>4097.39</v>
       </c>
       <c r="U111" s="15" t="n">
-        <v>-35.57999999999902</v>
+        <v>-11.85999999999967</v>
       </c>
       <c r="V111" s="13" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>4096.457142857143</v>
       </c>
       <c r="P112" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q112" s="6" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>4096.46</v>
       </c>
       <c r="U112" s="15" t="n">
-        <v>-35.48999999999978</v>
+        <v>-11.82999999999993</v>
       </c>
       <c r="V112" s="13" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>4095.528571428571</v>
       </c>
       <c r="P113" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q113" s="6" t="inlineStr">
         <is>
@@ -11484,7 +11484,7 @@
         <v>4095.53</v>
       </c>
       <c r="U113" s="15" t="n">
-        <v>-35.66999999999962</v>
+        <v>-11.88999999999987</v>
       </c>
       <c r="V113" s="13" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>4094.6</v>
       </c>
       <c r="P114" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q114" s="6" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
         <v>4094.6</v>
       </c>
       <c r="U114" s="15" t="n">
-        <v>-35.54999999999973</v>
+        <v>-11.84999999999991</v>
       </c>
       <c r="V114" s="13" t="inlineStr">
         <is>
@@ -11649,7 +11649,7 @@
         <v>4100.4</v>
       </c>
       <c r="P115" s="10" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q115" s="7" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>4131</v>
       </c>
       <c r="U115" s="9" t="n">
-        <v>34.05999999999949</v>
+        <v>17.02999999999975</v>
       </c>
       <c r="V115" s="20" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>4099.328571428571</v>
       </c>
       <c r="P116" s="10" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q116" s="7" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>4131</v>
       </c>
       <c r="U116" s="9" t="n">
-        <v>36.15999999999985</v>
+        <v>18.07999999999993</v>
       </c>
       <c r="V116" s="20" t="inlineStr">
         <is>
@@ -11835,7 +11835,7 @@
         <v>4098.257142857143</v>
       </c>
       <c r="P117" s="34" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q117" s="5" t="inlineStr">
         <is>
@@ -11912,7 +11912,7 @@
         <v>4097.185714285714</v>
       </c>
       <c r="P118" s="34" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q118" s="5" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>4096.114285714285</v>
       </c>
       <c r="P119" s="34" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q119" s="5" t="inlineStr">
         <is>
@@ -12066,7 +12066,7 @@
         <v>4095.042857142857</v>
       </c>
       <c r="P120" s="34" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q120" s="5" t="inlineStr">
         <is>
@@ -12143,7 +12143,7 @@
         <v>4093.971428571429</v>
       </c>
       <c r="P121" s="34" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q121" s="5" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>4092.9</v>
       </c>
       <c r="P122" s="34" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q122" s="5" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>4130.75</v>
       </c>
       <c r="P123" s="17" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q123" s="6" t="inlineStr">
         <is>
@@ -12318,7 +12318,7 @@
         <v>4130.75</v>
       </c>
       <c r="U123" s="15" t="n">
-        <v>-25.47999999999956</v>
+        <v>-12.73999999999978</v>
       </c>
       <c r="V123" s="13" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         <v>4131.75</v>
       </c>
       <c r="P124" s="17" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q124" s="6" t="inlineStr">
         <is>
@@ -12411,7 +12411,7 @@
         <v>4131.75</v>
       </c>
       <c r="U124" s="15" t="n">
-        <v>-25.5</v>
+        <v>-12.75</v>
       </c>
       <c r="V124" s="13" t="inlineStr">
         <is>
@@ -12483,7 +12483,7 @@
         <v>4132.75</v>
       </c>
       <c r="P125" s="17" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q125" s="6" t="inlineStr">
         <is>
@@ -12504,7 +12504,7 @@
         <v>4132.75</v>
       </c>
       <c r="U125" s="15" t="n">
-        <v>-25.42000000000008</v>
+        <v>-12.71000000000004</v>
       </c>
       <c r="V125" s="13" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>4133.75</v>
       </c>
       <c r="P126" s="41" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q126" s="8" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>4116.73</v>
       </c>
       <c r="U126" s="45" t="n">
-        <v>8.580000000001746</v>
+        <v>4.290000000000873</v>
       </c>
       <c r="V126" s="43" t="inlineStr">
         <is>
@@ -12669,7 +12669,7 @@
         <v>4134.75</v>
       </c>
       <c r="P127" s="41" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q127" s="8" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>4116.73</v>
       </c>
       <c r="U127" s="45" t="n">
-        <v>10.76000000000022</v>
+        <v>5.380000000000109</v>
       </c>
       <c r="V127" s="43" t="inlineStr">
         <is>
@@ -12762,7 +12762,7 @@
         <v>4135.75</v>
       </c>
       <c r="P128" s="41" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q128" s="8" t="inlineStr">
         <is>
@@ -12783,7 +12783,7 @@
         <v>4116.73</v>
       </c>
       <c r="U128" s="45" t="n">
-        <v>12.70000000000073</v>
+        <v>6.350000000000364</v>
       </c>
       <c r="V128" s="43" t="inlineStr">
         <is>
@@ -12849,13 +12849,13 @@
         <v>4100</v>
       </c>
       <c r="N129" s="40" t="n">
-        <v>4124.26</v>
+        <v>4124.21</v>
       </c>
       <c r="O129" s="40" t="n">
         <v>4136.75</v>
       </c>
       <c r="P129" s="41" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q129" s="8" t="inlineStr">
         <is>
@@ -12876,7 +12876,7 @@
         <v>4116.73</v>
       </c>
       <c r="U129" s="45" t="n">
-        <v>15.06000000000131</v>
+        <v>7.480000000000474</v>
       </c>
       <c r="V129" s="43" t="inlineStr">
         <is>
@@ -12948,7 +12948,7 @@
         <v>4137.75</v>
       </c>
       <c r="P130" s="41" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q130" s="8" t="inlineStr">
         <is>
@@ -12969,7 +12969,7 @@
         <v>4116.73</v>
       </c>
       <c r="U130" s="45" t="n">
-        <v>16.58000000000175</v>
+        <v>8.290000000000873</v>
       </c>
       <c r="V130" s="43" t="inlineStr">
         <is>
@@ -13041,7 +13041,7 @@
         <v>4090.1</v>
       </c>
       <c r="P131" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q131" s="7" t="inlineStr">
         <is>
@@ -13062,7 +13062,7 @@
         <v>4120</v>
       </c>
       <c r="U131" s="9" t="n">
-        <v>54.18000000000119</v>
+        <v>18.0600000000004</v>
       </c>
       <c r="V131" s="20" t="inlineStr">
         <is>
@@ -13134,7 +13134,7 @@
         <v>4089.171428571428</v>
       </c>
       <c r="P132" s="34" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q132" s="5" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>4088.242857142857</v>
       </c>
       <c r="P133" s="34" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q133" s="5" t="inlineStr">
         <is>
@@ -13288,7 +13288,7 @@
         <v>4087.314285714285</v>
       </c>
       <c r="P134" s="34" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q134" s="5" t="inlineStr">
         <is>
@@ -13365,7 +13365,7 @@
         <v>4086.385714285715</v>
       </c>
       <c r="P135" s="34" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q135" s="5" t="inlineStr">
         <is>
@@ -13442,7 +13442,7 @@
         <v>4085.457142857143</v>
       </c>
       <c r="P136" s="34" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q136" s="5" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
         <v>4084.528571428571</v>
       </c>
       <c r="P137" s="34" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q137" s="5" t="inlineStr">
         <is>
@@ -13596,7 +13596,7 @@
         <v>4083.6</v>
       </c>
       <c r="P138" s="34" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q138" s="5" t="inlineStr">
         <is>
@@ -13673,7 +13673,7 @@
         <v>4140.75</v>
       </c>
       <c r="P139" s="10" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q139" s="7" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         <v>4110</v>
       </c>
       <c r="U139" s="9" t="n">
-        <v>36.10000000000036</v>
+        <v>18.05000000000018</v>
       </c>
       <c r="V139" s="20" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>4141.75</v>
       </c>
       <c r="P140" s="10" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q140" s="7" t="inlineStr">
         <is>
@@ -13787,7 +13787,7 @@
         <v>4110</v>
       </c>
       <c r="U140" s="9" t="n">
-        <v>38.1200000000008</v>
+        <v>19.0600000000004</v>
       </c>
       <c r="V140" s="20" t="inlineStr">
         <is>
@@ -13859,7 +13859,7 @@
         <v>4142.75</v>
       </c>
       <c r="P141" s="10" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q141" s="7" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>4110</v>
       </c>
       <c r="U141" s="9" t="n">
-        <v>40.02000000000044</v>
+        <v>20.01000000000022</v>
       </c>
       <c r="V141" s="20" t="inlineStr">
         <is>
@@ -13952,7 +13952,7 @@
         <v>4143.75</v>
       </c>
       <c r="P142" s="10" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q142" s="7" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         <v>4110</v>
       </c>
       <c r="U142" s="9" t="n">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="V142" s="20" t="inlineStr">
         <is>
@@ -14045,7 +14045,7 @@
         <v>4144.75</v>
       </c>
       <c r="P143" s="10" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q143" s="7" t="inlineStr">
         <is>
@@ -14066,7 +14066,7 @@
         <v>4110</v>
       </c>
       <c r="U143" s="9" t="n">
-        <v>44.02000000000044</v>
+        <v>22.01000000000022</v>
       </c>
       <c r="V143" s="20" t="inlineStr">
         <is>
@@ -14138,7 +14138,7 @@
         <v>4145.75</v>
       </c>
       <c r="P144" s="10" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q144" s="7" t="inlineStr">
         <is>
@@ -14159,7 +14159,7 @@
         <v>4110</v>
       </c>
       <c r="U144" s="9" t="n">
-        <v>46.02000000000044</v>
+        <v>23.01000000000022</v>
       </c>
       <c r="V144" s="20" t="inlineStr">
         <is>
@@ -14231,7 +14231,7 @@
         <v>4146.75</v>
       </c>
       <c r="P145" s="34" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q145" s="5" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         <v>4147.75</v>
       </c>
       <c r="P146" s="34" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q146" s="5" t="inlineStr">
         <is>
@@ -14385,7 +14385,7 @@
         <v>4101.1</v>
       </c>
       <c r="P147" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q147" s="7" t="inlineStr">
         <is>
@@ -14406,7 +14406,7 @@
         <v>4131</v>
       </c>
       <c r="U147" s="9" t="n">
-        <v>54.42000000000098</v>
+        <v>18.14000000000033</v>
       </c>
       <c r="V147" s="20" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>4100.171428571429</v>
       </c>
       <c r="P148" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q148" s="7" t="inlineStr">
         <is>
@@ -14499,7 +14499,7 @@
         <v>4131</v>
       </c>
       <c r="U148" s="9" t="n">
-        <v>57.06000000000131</v>
+        <v>19.02000000000044</v>
       </c>
       <c r="V148" s="20" t="inlineStr">
         <is>
@@ -14571,7 +14571,7 @@
         <v>4099.242857142857</v>
       </c>
       <c r="P149" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q149" s="7" t="inlineStr">
         <is>
@@ -14592,7 +14592,7 @@
         <v>4131</v>
       </c>
       <c r="U149" s="9" t="n">
-        <v>59.60999999999967</v>
+        <v>19.86999999999989</v>
       </c>
       <c r="V149" s="20" t="inlineStr">
         <is>
@@ -14664,7 +14664,7 @@
         <v>4098.314285714286</v>
       </c>
       <c r="P150" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q150" s="7" t="inlineStr">
         <is>
@@ -14685,7 +14685,7 @@
         <v>4131</v>
       </c>
       <c r="U150" s="9" t="n">
-        <v>62.79000000000087</v>
+        <v>20.93000000000029</v>
       </c>
       <c r="V150" s="20" t="inlineStr">
         <is>
@@ -14757,7 +14757,7 @@
         <v>4097.385714285715</v>
       </c>
       <c r="P151" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q151" s="7" t="inlineStr">
         <is>
@@ -14778,7 +14778,7 @@
         <v>4131</v>
       </c>
       <c r="U151" s="9" t="n">
-        <v>65.13000000000011</v>
+        <v>21.71000000000004</v>
       </c>
       <c r="V151" s="20" t="inlineStr">
         <is>
@@ -14850,7 +14850,7 @@
         <v>4096.457142857143</v>
       </c>
       <c r="P152" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q152" s="7" t="inlineStr">
         <is>
@@ -14871,7 +14871,7 @@
         <v>4131</v>
       </c>
       <c r="U152" s="9" t="n">
-        <v>67.97999999999956</v>
+        <v>22.65999999999985</v>
       </c>
       <c r="V152" s="20" t="inlineStr">
         <is>
@@ -14943,7 +14943,7 @@
         <v>4095.528571428571</v>
       </c>
       <c r="P153" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q153" s="7" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
         <v>4131</v>
       </c>
       <c r="U153" s="9" t="n">
-        <v>71.09999999999945</v>
+        <v>23.69999999999982</v>
       </c>
       <c r="V153" s="20" t="inlineStr">
         <is>
@@ -15036,7 +15036,7 @@
         <v>4094.6</v>
       </c>
       <c r="P154" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q154" s="7" t="inlineStr">
         <is>
@@ -15057,7 +15057,7 @@
         <v>4131</v>
       </c>
       <c r="U154" s="9" t="n">
-        <v>73.5</v>
+        <v>24.5</v>
       </c>
       <c r="V154" s="20" t="inlineStr">
         <is>
@@ -15129,7 +15129,7 @@
         <v>4100.1</v>
       </c>
       <c r="P155" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q155" s="7" t="inlineStr">
         <is>
@@ -15150,7 +15150,7 @@
         <v>4130</v>
       </c>
       <c r="U155" s="9" t="n">
-        <v>54.06000000000131</v>
+        <v>18.02000000000044</v>
       </c>
       <c r="V155" s="20" t="inlineStr">
         <is>
@@ -15222,7 +15222,7 @@
         <v>4099.171428571429</v>
       </c>
       <c r="P156" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q156" s="7" t="inlineStr">
         <is>
@@ -15243,7 +15243,7 @@
         <v>4130</v>
       </c>
       <c r="U156" s="9" t="n">
-        <v>56.79000000000087</v>
+        <v>18.93000000000029</v>
       </c>
       <c r="V156" s="20" t="inlineStr">
         <is>
@@ -15315,7 +15315,7 @@
         <v>4098.242857142857</v>
       </c>
       <c r="P157" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q157" s="7" t="inlineStr">
         <is>
@@ -15336,7 +15336,7 @@
         <v>4130</v>
       </c>
       <c r="U157" s="9" t="n">
-        <v>59.79000000000087</v>
+        <v>19.93000000000029</v>
       </c>
       <c r="V157" s="20" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>4097.314285714286</v>
       </c>
       <c r="P158" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q158" s="7" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>4130</v>
       </c>
       <c r="U158" s="9" t="n">
-        <v>62.36999999999989</v>
+        <v>20.78999999999996</v>
       </c>
       <c r="V158" s="20" t="inlineStr">
         <is>
@@ -15495,13 +15495,13 @@
         <v>4130</v>
       </c>
       <c r="N159" s="39" t="n">
-        <v>4108.29</v>
+        <v>4108.28</v>
       </c>
       <c r="O159" s="39" t="n">
         <v>4096.385714285715</v>
       </c>
       <c r="P159" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q159" s="7" t="inlineStr">
         <is>
@@ -15522,7 +15522,7 @@
         <v>4130</v>
       </c>
       <c r="U159" s="9" t="n">
-        <v>65.13000000000011</v>
+        <v>21.72000000000025</v>
       </c>
       <c r="V159" s="20" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
       </c>
       <c r="W159" s="21" t="inlineStr">
         <is>
-          <t>1:1.82</t>
+          <t>1:1.83</t>
         </is>
       </c>
     </row>
@@ -15594,7 +15594,7 @@
         <v>4095.457142857143</v>
       </c>
       <c r="P160" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q160" s="7" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         <v>4130</v>
       </c>
       <c r="U160" s="9" t="n">
-        <v>68.09999999999945</v>
+        <v>22.69999999999982</v>
       </c>
       <c r="V160" s="20" t="inlineStr">
         <is>
@@ -15687,7 +15687,7 @@
         <v>4094.528571428571</v>
       </c>
       <c r="P161" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q161" s="7" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>4130</v>
       </c>
       <c r="U161" s="9" t="n">
-        <v>70.73999999999978</v>
+        <v>23.57999999999993</v>
       </c>
       <c r="V161" s="20" t="inlineStr">
         <is>
@@ -15774,13 +15774,13 @@
         <v>4130</v>
       </c>
       <c r="N162" s="39" t="n">
-        <v>4105.49</v>
+        <v>4105.5</v>
       </c>
       <c r="O162" s="39" t="n">
         <v>4093.6</v>
       </c>
       <c r="P162" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q162" s="7" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>4130</v>
       </c>
       <c r="U162" s="9" t="n">
-        <v>73.53000000000065</v>
+        <v>24.5</v>
       </c>
       <c r="V162" s="20" t="inlineStr">
         <is>
@@ -15873,7 +15873,7 @@
         <v>4105.1</v>
       </c>
       <c r="P163" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q163" s="6" t="inlineStr">
         <is>
@@ -15894,7 +15894,7 @@
         <v>4105.1</v>
       </c>
       <c r="U163" s="15" t="n">
-        <v>-35.6399999999976</v>
+        <v>-11.8799999999992</v>
       </c>
       <c r="V163" s="13" t="inlineStr">
         <is>
@@ -15966,7 +15966,7 @@
         <v>4104.171428571429</v>
       </c>
       <c r="P164" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q164" s="7" t="inlineStr">
         <is>
@@ -15987,7 +15987,7 @@
         <v>4135</v>
       </c>
       <c r="U164" s="9" t="n">
-        <v>56.93999999999869</v>
+        <v>18.97999999999956</v>
       </c>
       <c r="V164" s="20" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>4103.242857142857</v>
       </c>
       <c r="P165" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q165" s="7" t="inlineStr">
         <is>
@@ -16080,7 +16080,7 @@
         <v>4135</v>
       </c>
       <c r="U165" s="9" t="n">
-        <v>59.67000000000098</v>
+        <v>19.89000000000033</v>
       </c>
       <c r="V165" s="20" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
         <v>4102.314285714286</v>
       </c>
       <c r="P166" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q166" s="7" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>4135</v>
       </c>
       <c r="U166" s="9" t="n">
-        <v>62.52000000000043</v>
+        <v>20.84000000000015</v>
       </c>
       <c r="V166" s="20" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         <v>4101.385714285715</v>
       </c>
       <c r="P167" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q167" s="7" t="inlineStr">
         <is>
@@ -16266,7 +16266,7 @@
         <v>4135</v>
       </c>
       <c r="U167" s="9" t="n">
-        <v>65.72999999999956</v>
+        <v>21.90999999999985</v>
       </c>
       <c r="V167" s="20" t="inlineStr">
         <is>
@@ -16338,7 +16338,7 @@
         <v>4100.457142857143</v>
       </c>
       <c r="P168" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q168" s="7" t="inlineStr">
         <is>
@@ -16359,7 +16359,7 @@
         <v>4135</v>
       </c>
       <c r="U168" s="9" t="n">
-        <v>67.92000000000098</v>
+        <v>22.64000000000033</v>
       </c>
       <c r="V168" s="20" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>4099.528571428572</v>
       </c>
       <c r="P169" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q169" s="7" t="inlineStr">
         <is>
@@ -16452,7 +16452,7 @@
         <v>4135</v>
       </c>
       <c r="U169" s="9" t="n">
-        <v>70.73999999999978</v>
+        <v>23.57999999999993</v>
       </c>
       <c r="V169" s="20" t="inlineStr">
         <is>
@@ -16524,7 +16524,7 @@
         <v>4098.6</v>
       </c>
       <c r="P170" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q170" s="7" t="inlineStr">
         <is>
@@ -16545,7 +16545,7 @@
         <v>4135</v>
       </c>
       <c r="U170" s="9" t="n">
-        <v>73.5600000000013</v>
+        <v>24.52000000000044</v>
       </c>
       <c r="V170" s="20" t="inlineStr">
         <is>
@@ -16617,7 +16617,7 @@
         <v>4105.1</v>
       </c>
       <c r="P171" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q171" s="5" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>4104.171428571429</v>
       </c>
       <c r="P172" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q172" s="5" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
         <v>4103.242857142857</v>
       </c>
       <c r="P173" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q173" s="5" t="inlineStr">
         <is>
@@ -16848,7 +16848,7 @@
         <v>4102.314285714286</v>
       </c>
       <c r="P174" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q174" s="5" t="inlineStr">
         <is>
@@ -16925,7 +16925,7 @@
         <v>4101.385714285715</v>
       </c>
       <c r="P175" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q175" s="5" t="inlineStr">
         <is>
@@ -17002,7 +17002,7 @@
         <v>4100.457142857143</v>
       </c>
       <c r="P176" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q176" s="5" t="inlineStr">
         <is>
@@ -17079,7 +17079,7 @@
         <v>4099.528571428572</v>
       </c>
       <c r="P177" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q177" s="5" t="inlineStr">
         <is>
@@ -17156,7 +17156,7 @@
         <v>4098.6</v>
       </c>
       <c r="P178" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q178" s="5" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         <v>4112.1</v>
       </c>
       <c r="P179" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q179" s="7" t="inlineStr">
         <is>
@@ -17254,7 +17254,7 @@
         <v>4141</v>
       </c>
       <c r="U179" s="9" t="n">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="V179" s="20" t="inlineStr">
         <is>
@@ -17326,7 +17326,7 @@
         <v>4111.171428571429</v>
       </c>
       <c r="P180" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q180" s="5" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         <v>4110.242857142857</v>
       </c>
       <c r="P181" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q181" s="5" t="inlineStr">
         <is>
@@ -17480,7 +17480,7 @@
         <v>4109.314285714286</v>
       </c>
       <c r="P182" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q182" s="5" t="inlineStr">
         <is>
@@ -17557,7 +17557,7 @@
         <v>4108.385714285715</v>
       </c>
       <c r="P183" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q183" s="5" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>4107.457142857143</v>
       </c>
       <c r="P184" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q184" s="5" t="inlineStr">
         <is>
@@ -17711,7 +17711,7 @@
         <v>4106.528571428572</v>
       </c>
       <c r="P185" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q185" s="5" t="inlineStr">
         <is>
@@ -17788,7 +17788,7 @@
         <v>4105.6</v>
       </c>
       <c r="P186" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q186" s="5" t="inlineStr">
         <is>
@@ -17865,7 +17865,7 @@
         <v>4108.1</v>
       </c>
       <c r="P187" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q187" s="5" t="inlineStr">
         <is>
@@ -17942,7 +17942,7 @@
         <v>4107.171428571429</v>
       </c>
       <c r="P188" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q188" s="5" t="inlineStr">
         <is>
@@ -18019,7 +18019,7 @@
         <v>4106.242857142857</v>
       </c>
       <c r="P189" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q189" s="5" t="inlineStr">
         <is>
@@ -18096,7 +18096,7 @@
         <v>4105.314285714286</v>
       </c>
       <c r="P190" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q190" s="5" t="inlineStr">
         <is>
@@ -18173,7 +18173,7 @@
         <v>4104.385714285715</v>
       </c>
       <c r="P191" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q191" s="5" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>4103.457142857143</v>
       </c>
       <c r="P192" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q192" s="5" t="inlineStr">
         <is>
@@ -18327,7 +18327,7 @@
         <v>4102.528571428572</v>
       </c>
       <c r="P193" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q193" s="5" t="inlineStr">
         <is>
@@ -18404,7 +18404,7 @@
         <v>4101.6</v>
       </c>
       <c r="P194" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q194" s="5" t="inlineStr">
         <is>
@@ -18481,7 +18481,7 @@
         <v>4043.1</v>
       </c>
       <c r="P195" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q195" s="5" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
         <v>4042.171428571428</v>
       </c>
       <c r="P196" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q196" s="5" t="inlineStr">
         <is>
@@ -18635,7 +18635,7 @@
         <v>4041.242857142857</v>
       </c>
       <c r="P197" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q197" s="5" t="inlineStr">
         <is>
@@ -18712,7 +18712,7 @@
         <v>4040.314285714286</v>
       </c>
       <c r="P198" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q198" s="5" t="inlineStr">
         <is>
@@ -18789,7 +18789,7 @@
         <v>4039.385714285714</v>
       </c>
       <c r="P199" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q199" s="5" t="inlineStr">
         <is>
@@ -18866,7 +18866,7 @@
         <v>4038.457142857143</v>
       </c>
       <c r="P200" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q200" s="5" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>4037.528571428571</v>
       </c>
       <c r="P201" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q201" s="5" t="inlineStr">
         <is>
@@ -19020,7 +19020,7 @@
         <v>4036.6</v>
       </c>
       <c r="P202" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q202" s="5" t="inlineStr">
         <is>
@@ -19097,7 +19097,7 @@
         <v>4104.9</v>
       </c>
       <c r="P203" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q203" s="7" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>4078</v>
       </c>
       <c r="U203" s="9" t="n">
-        <v>44.99999999999999</v>
+        <v>15</v>
       </c>
       <c r="V203" s="20" t="inlineStr">
         <is>
@@ -19190,7 +19190,7 @@
         <v>4105.828571428571</v>
       </c>
       <c r="P204" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q204" s="7" t="inlineStr">
         <is>
@@ -19211,7 +19211,7 @@
         <v>4078</v>
       </c>
       <c r="U204" s="9" t="n">
-        <v>47.82000000000016</v>
+        <v>15.94000000000005</v>
       </c>
       <c r="V204" s="20" t="inlineStr">
         <is>
@@ -19283,7 +19283,7 @@
         <v>4106.757142857143</v>
       </c>
       <c r="P205" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q205" s="5" t="inlineStr">
         <is>
@@ -19360,7 +19360,7 @@
         <v>4107.685714285714</v>
       </c>
       <c r="P206" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q206" s="5" t="inlineStr">
         <is>
@@ -19437,7 +19437,7 @@
         <v>4108.614285714285</v>
       </c>
       <c r="P207" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q207" s="5" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>4109.542857142857</v>
       </c>
       <c r="P208" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q208" s="5" t="inlineStr">
         <is>
@@ -19591,7 +19591,7 @@
         <v>4110.471428571428</v>
       </c>
       <c r="P209" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q209" s="5" t="inlineStr">
         <is>
@@ -19668,7 +19668,7 @@
         <v>4111.4</v>
       </c>
       <c r="P210" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q210" s="5" t="inlineStr">
         <is>
@@ -19745,7 +19745,7 @@
         <v>4063.1</v>
       </c>
       <c r="P211" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q211" s="6" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
         <v>4063.1</v>
       </c>
       <c r="U211" s="15" t="n">
-        <v>-35.70000000000027</v>
+        <v>-11.90000000000009</v>
       </c>
       <c r="V211" s="13" t="inlineStr">
         <is>
@@ -19838,7 +19838,7 @@
         <v>4062.171428571428</v>
       </c>
       <c r="P212" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q212" s="6" t="inlineStr">
         <is>
@@ -19859,7 +19859,7 @@
         <v>4062.17</v>
       </c>
       <c r="U212" s="15" t="n">
-        <v>-35.70000000000027</v>
+        <v>-11.90000000000009</v>
       </c>
       <c r="V212" s="13" t="inlineStr">
         <is>
@@ -19931,7 +19931,7 @@
         <v>4061.242857142857</v>
       </c>
       <c r="P213" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q213" s="6" t="inlineStr">
         <is>
@@ -19952,7 +19952,7 @@
         <v>4061.24</v>
       </c>
       <c r="U213" s="15" t="n">
-        <v>-35.3400000000006</v>
+        <v>-11.7800000000002</v>
       </c>
       <c r="V213" s="13" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>4060.314285714286</v>
       </c>
       <c r="P214" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q214" s="6" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>4060.31</v>
       </c>
       <c r="U214" s="15" t="n">
-        <v>-35.54999999999973</v>
+        <v>-11.84999999999991</v>
       </c>
       <c r="V214" s="13" t="inlineStr">
         <is>
@@ -20111,13 +20111,13 @@
         <v>4090</v>
       </c>
       <c r="N215" s="38" t="n">
-        <v>4071.18</v>
+        <v>4071.23</v>
       </c>
       <c r="O215" s="38" t="n">
         <v>4059.385714285714</v>
       </c>
       <c r="P215" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q215" s="6" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>4059.39</v>
       </c>
       <c r="U215" s="15" t="n">
-        <v>-35.36999999999989</v>
+        <v>-11.84000000000015</v>
       </c>
       <c r="V215" s="13" t="inlineStr">
         <is>
@@ -20210,7 +20210,7 @@
         <v>4058.457142857143</v>
       </c>
       <c r="P216" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q216" s="6" t="inlineStr">
         <is>
@@ -20231,7 +20231,7 @@
         <v>4058.46</v>
       </c>
       <c r="U216" s="15" t="n">
-        <v>-35.40000000000055</v>
+        <v>-11.80000000000018</v>
       </c>
       <c r="V216" s="13" t="inlineStr">
         <is>
@@ -20303,7 +20303,7 @@
         <v>4057.528571428571</v>
       </c>
       <c r="P217" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q217" s="6" t="inlineStr">
         <is>
@@ -20324,7 +20324,7 @@
         <v>4057.53</v>
       </c>
       <c r="U217" s="15" t="n">
-        <v>-35.66999999999962</v>
+        <v>-11.88999999999987</v>
       </c>
       <c r="V217" s="13" t="inlineStr">
         <is>
@@ -20396,7 +20396,7 @@
         <v>4056.6</v>
       </c>
       <c r="P218" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q218" s="6" t="inlineStr">
         <is>
@@ -20417,7 +20417,7 @@
         <v>4056.6</v>
       </c>
       <c r="U218" s="15" t="n">
-        <v>-35.48999999999978</v>
+        <v>-11.82999999999993</v>
       </c>
       <c r="V218" s="13" t="inlineStr">
         <is>
@@ -20489,7 +20489,7 @@
         <v>4068.1</v>
       </c>
       <c r="P219" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q219" s="6" t="inlineStr">
         <is>
@@ -20510,7 +20510,7 @@
         <v>4068.1</v>
       </c>
       <c r="U219" s="15" t="n">
-        <v>-35.66999999999962</v>
+        <v>-11.88999999999987</v>
       </c>
       <c r="V219" s="13" t="inlineStr">
         <is>
@@ -20582,7 +20582,7 @@
         <v>4067.171428571428</v>
       </c>
       <c r="P220" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q220" s="6" t="inlineStr">
         <is>
@@ -20603,7 +20603,7 @@
         <v>4067.17</v>
       </c>
       <c r="U220" s="15" t="n">
-        <v>-35.60999999999967</v>
+        <v>-11.86999999999989</v>
       </c>
       <c r="V220" s="13" t="inlineStr">
         <is>
@@ -20675,7 +20675,7 @@
         <v>4066.242857142857</v>
       </c>
       <c r="P221" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q221" s="6" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>4066.24</v>
       </c>
       <c r="U221" s="15" t="n">
-        <v>-35.67000000000098</v>
+        <v>-11.89000000000033</v>
       </c>
       <c r="V221" s="13" t="inlineStr">
         <is>
@@ -20768,7 +20768,7 @@
         <v>4065.314285714286</v>
       </c>
       <c r="P222" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q222" s="6" t="inlineStr">
         <is>
@@ -20789,7 +20789,7 @@
         <v>4065.31</v>
       </c>
       <c r="U222" s="15" t="n">
-        <v>-35.28000000000065</v>
+        <v>-11.76000000000022</v>
       </c>
       <c r="V222" s="13" t="inlineStr">
         <is>
@@ -20861,7 +20861,7 @@
         <v>4064.385714285714</v>
       </c>
       <c r="P223" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q223" s="6" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>4064.39</v>
       </c>
       <c r="U223" s="15" t="n">
-        <v>-35.64000000000033</v>
+        <v>-11.88000000000011</v>
       </c>
       <c r="V223" s="13" t="inlineStr">
         <is>
@@ -20954,7 +20954,7 @@
         <v>4063.457142857143</v>
       </c>
       <c r="P224" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q224" s="6" t="inlineStr">
         <is>
@@ -20975,7 +20975,7 @@
         <v>4063.46</v>
       </c>
       <c r="U224" s="15" t="n">
-        <v>-35.42999999999984</v>
+        <v>-11.80999999999995</v>
       </c>
       <c r="V224" s="13" t="inlineStr">
         <is>
@@ -21047,7 +21047,7 @@
         <v>4062.528571428571</v>
       </c>
       <c r="P225" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q225" s="6" t="inlineStr">
         <is>
@@ -21068,7 +21068,7 @@
         <v>4062.53</v>
       </c>
       <c r="U225" s="15" t="n">
-        <v>-35.57999999999902</v>
+        <v>-11.85999999999967</v>
       </c>
       <c r="V225" s="13" t="inlineStr">
         <is>
@@ -21140,7 +21140,7 @@
         <v>4061.6</v>
       </c>
       <c r="P226" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q226" s="6" t="inlineStr">
         <is>
@@ -21161,7 +21161,7 @@
         <v>4061.6</v>
       </c>
       <c r="U226" s="15" t="n">
-        <v>-35.30999999999994</v>
+        <v>-11.76999999999998</v>
       </c>
       <c r="V226" s="13" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>3973.1</v>
       </c>
       <c r="P227" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q227" s="6" t="inlineStr">
         <is>
@@ -21254,7 +21254,7 @@
         <v>3973.1</v>
       </c>
       <c r="U227" s="15" t="n">
-        <v>-35.70000000000027</v>
+        <v>-11.90000000000009</v>
       </c>
       <c r="V227" s="13" t="inlineStr">
         <is>
@@ -21326,7 +21326,7 @@
         <v>3972.171428571428</v>
       </c>
       <c r="P228" s="17" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q228" s="6" t="inlineStr">
         <is>
@@ -21347,7 +21347,7 @@
         <v>3972.17</v>
       </c>
       <c r="U228" s="15" t="n">
-        <v>-35.45999999999913</v>
+        <v>-11.81999999999971</v>
       </c>
       <c r="V228" s="13" t="inlineStr">
         <is>
@@ -21419,7 +21419,7 @@
         <v>3971.242857142857</v>
       </c>
       <c r="P229" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q229" s="7" t="inlineStr">
         <is>
@@ -21440,7 +21440,7 @@
         <v>4000</v>
       </c>
       <c r="U229" s="9" t="n">
-        <v>51.05999999999994</v>
+        <v>17.01999999999998</v>
       </c>
       <c r="V229" s="20" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
         <v>3970.314285714286</v>
       </c>
       <c r="P230" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q230" s="7" t="inlineStr">
         <is>
@@ -21533,7 +21533,7 @@
         <v>4000</v>
       </c>
       <c r="U230" s="9" t="n">
-        <v>53.54999999999972</v>
+        <v>17.84999999999991</v>
       </c>
       <c r="V230" s="20" t="inlineStr">
         <is>
@@ -21605,7 +21605,7 @@
         <v>3969.385714285714</v>
       </c>
       <c r="P231" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q231" s="7" t="inlineStr">
         <is>
@@ -21626,7 +21626,7 @@
         <v>4000</v>
       </c>
       <c r="U231" s="9" t="n">
-        <v>56.1300000000001</v>
+        <v>18.71000000000004</v>
       </c>
       <c r="V231" s="20" t="inlineStr">
         <is>
@@ -21698,7 +21698,7 @@
         <v>3968.457142857143</v>
       </c>
       <c r="P232" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q232" s="7" t="inlineStr">
         <is>
@@ -21719,7 +21719,7 @@
         <v>4000</v>
       </c>
       <c r="U232" s="9" t="n">
-        <v>59.21999999999934</v>
+        <v>19.73999999999978</v>
       </c>
       <c r="V232" s="20" t="inlineStr">
         <is>
@@ -21791,7 +21791,7 @@
         <v>3967.528571428571</v>
       </c>
       <c r="P233" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q233" s="7" t="inlineStr">
         <is>
@@ -21812,7 +21812,7 @@
         <v>4000</v>
       </c>
       <c r="U233" s="9" t="n">
-        <v>61.83000000000038</v>
+        <v>20.61000000000013</v>
       </c>
       <c r="V233" s="20" t="inlineStr">
         <is>
@@ -21884,7 +21884,7 @@
         <v>3966.6</v>
       </c>
       <c r="P234" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q234" s="7" t="inlineStr">
         <is>
@@ -21905,7 +21905,7 @@
         <v>4000</v>
       </c>
       <c r="U234" s="9" t="n">
-        <v>64.5</v>
+        <v>21.5</v>
       </c>
       <c r="V234" s="20" t="inlineStr">
         <is>
@@ -21977,7 +21977,7 @@
         <v>3961.1</v>
       </c>
       <c r="P235" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q235" s="7" t="inlineStr">
         <is>
@@ -21998,7 +21998,7 @@
         <v>3988</v>
       </c>
       <c r="U235" s="9" t="n">
-        <v>45.09000000000059</v>
+        <v>15.0300000000002</v>
       </c>
       <c r="V235" s="20" t="inlineStr">
         <is>
@@ -22070,7 +22070,7 @@
         <v>3960.171428571428</v>
       </c>
       <c r="P236" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q236" s="7" t="inlineStr">
         <is>
@@ -22091,7 +22091,7 @@
         <v>3988</v>
       </c>
       <c r="U236" s="9" t="n">
-        <v>47.7899999999995</v>
+        <v>15.92999999999984</v>
       </c>
       <c r="V236" s="20" t="inlineStr">
         <is>
@@ -22163,7 +22163,7 @@
         <v>3959.242857142857</v>
       </c>
       <c r="P237" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q237" s="5" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>3958.314285714286</v>
       </c>
       <c r="P238" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q238" s="5" t="inlineStr">
         <is>
@@ -22317,7 +22317,7 @@
         <v>3957.385714285714</v>
       </c>
       <c r="P239" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q239" s="5" t="inlineStr">
         <is>
@@ -22394,7 +22394,7 @@
         <v>3956.457142857143</v>
       </c>
       <c r="P240" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q240" s="5" t="inlineStr">
         <is>
@@ -22471,7 +22471,7 @@
         <v>3955.528571428571</v>
       </c>
       <c r="P241" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q241" s="5" t="inlineStr">
         <is>
@@ -22548,7 +22548,7 @@
         <v>3954.6</v>
       </c>
       <c r="P242" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q242" s="5" t="inlineStr">
         <is>
@@ -22625,7 +22625,7 @@
         <v>3968.1</v>
       </c>
       <c r="P243" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q243" s="7" t="inlineStr">
         <is>
@@ -22646,7 +22646,7 @@
         <v>3995</v>
       </c>
       <c r="U243" s="9" t="n">
-        <v>45.41999999999962</v>
+        <v>15.13999999999987</v>
       </c>
       <c r="V243" s="20" t="inlineStr">
         <is>
@@ -22718,7 +22718,7 @@
         <v>3967.171428571428</v>
       </c>
       <c r="P244" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q244" s="7" t="inlineStr">
         <is>
@@ -22739,7 +22739,7 @@
         <v>3995</v>
       </c>
       <c r="U244" s="9" t="n">
-        <v>47.96999999999934</v>
+        <v>15.98999999999978</v>
       </c>
       <c r="V244" s="20" t="inlineStr">
         <is>
@@ -22811,7 +22811,7 @@
         <v>3966.242857142857</v>
       </c>
       <c r="P245" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q245" s="7" t="inlineStr">
         <is>
@@ -22832,7 +22832,7 @@
         <v>3995</v>
       </c>
       <c r="U245" s="9" t="n">
-        <v>50.60999999999967</v>
+        <v>16.86999999999989</v>
       </c>
       <c r="V245" s="20" t="inlineStr">
         <is>
@@ -22904,7 +22904,7 @@
         <v>3965.314285714286</v>
       </c>
       <c r="P246" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q246" s="7" t="inlineStr">
         <is>
@@ -22925,7 +22925,7 @@
         <v>3995</v>
       </c>
       <c r="U246" s="9" t="n">
-        <v>53.42999999999984</v>
+        <v>17.80999999999995</v>
       </c>
       <c r="V246" s="20" t="inlineStr">
         <is>
@@ -22997,7 +22997,7 @@
         <v>3964.385714285714</v>
       </c>
       <c r="P247" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q247" s="7" t="inlineStr">
         <is>
@@ -23018,7 +23018,7 @@
         <v>3995</v>
       </c>
       <c r="U247" s="9" t="n">
-        <v>56.1599999999994</v>
+        <v>18.7199999999998</v>
       </c>
       <c r="V247" s="20" t="inlineStr">
         <is>
@@ -23090,7 +23090,7 @@
         <v>3963.457142857143</v>
       </c>
       <c r="P248" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q248" s="7" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
         <v>3995</v>
       </c>
       <c r="U248" s="9" t="n">
-        <v>59.0399999999995</v>
+        <v>19.67999999999984</v>
       </c>
       <c r="V248" s="20" t="inlineStr">
         <is>
@@ -23183,7 +23183,7 @@
         <v>3962.528571428571</v>
       </c>
       <c r="P249" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q249" s="7" t="inlineStr">
         <is>
@@ -23204,7 +23204,7 @@
         <v>3995</v>
       </c>
       <c r="U249" s="9" t="n">
-        <v>61.85999999999967</v>
+        <v>20.61999999999989</v>
       </c>
       <c r="V249" s="20" t="inlineStr">
         <is>
@@ -23276,7 +23276,7 @@
         <v>3961.6</v>
       </c>
       <c r="P250" s="10" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q250" s="7" t="inlineStr">
         <is>
@@ -23297,7 +23297,7 @@
         <v>3995</v>
       </c>
       <c r="U250" s="9" t="n">
-        <v>64.55999999999995</v>
+        <v>21.51999999999998</v>
       </c>
       <c r="V250" s="20" t="inlineStr">
         <is>
@@ -23369,7 +23369,7 @@
         <v>3958.1</v>
       </c>
       <c r="P251" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q251" s="5" t="inlineStr">
         <is>
@@ -23446,7 +23446,7 @@
         <v>3957.171428571428</v>
       </c>
       <c r="P252" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q252" s="5" t="inlineStr">
         <is>
@@ -23523,7 +23523,7 @@
         <v>3956.242857142857</v>
       </c>
       <c r="P253" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q253" s="5" t="inlineStr">
         <is>
@@ -23600,7 +23600,7 @@
         <v>3955.314285714286</v>
       </c>
       <c r="P254" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q254" s="5" t="inlineStr">
         <is>
@@ -23677,7 +23677,7 @@
         <v>3954.385714285714</v>
       </c>
       <c r="P255" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q255" s="5" t="inlineStr">
         <is>
@@ -23754,7 +23754,7 @@
         <v>3953.457142857143</v>
       </c>
       <c r="P256" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q256" s="5" t="inlineStr">
         <is>
@@ -23831,7 +23831,7 @@
         <v>3952.528571428571</v>
       </c>
       <c r="P257" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q257" s="5" t="inlineStr">
         <is>
@@ -23908,7 +23908,7 @@
         <v>3951.6</v>
       </c>
       <c r="P258" s="34" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q258" s="5" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         <v>4010.75</v>
       </c>
       <c r="P259" s="10" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q259" s="7" t="inlineStr">
         <is>
@@ -24006,7 +24006,7 @@
         <v>3983</v>
       </c>
       <c r="U259" s="9" t="n">
-        <v>30.03999999999997</v>
+        <v>15.01999999999998</v>
       </c>
       <c r="V259" s="20" t="inlineStr">
         <is>
@@ -24078,7 +24078,7 @@
         <v>4011.75</v>
       </c>
       <c r="P260" s="10" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q260" s="7" t="inlineStr">
         <is>
@@ -24099,7 +24099,7 @@
         <v>3983</v>
       </c>
       <c r="U260" s="9" t="n">
-        <v>32.22000000000025</v>
+        <v>16.11000000000013</v>
       </c>
       <c r="V260" s="20" t="inlineStr">
         <is>
@@ -24171,7 +24171,7 @@
         <v>4012.75</v>
       </c>
       <c r="P261" s="10" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q261" s="7" t="inlineStr">
         <is>
@@ -24192,7 +24192,7 @@
         <v>3983</v>
       </c>
       <c r="U261" s="9" t="n">
-        <v>34.26000000000022</v>
+        <v>17.13000000000011</v>
       </c>
       <c r="V261" s="20" t="inlineStr">
         <is>
@@ -24264,7 +24264,7 @@
         <v>4013.75</v>
       </c>
       <c r="P262" s="10" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q262" s="7" t="inlineStr">
         <is>
@@ -24285,7 +24285,7 @@
         <v>3983</v>
       </c>
       <c r="U262" s="9" t="n">
-        <v>36.10000000000036</v>
+        <v>18.05000000000018</v>
       </c>
       <c r="V262" s="20" t="inlineStr">
         <is>
@@ -24357,7 +24357,7 @@
         <v>4014.75</v>
       </c>
       <c r="P263" s="10" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q263" s="7" t="inlineStr">
         <is>
@@ -24378,7 +24378,7 @@
         <v>3983</v>
       </c>
       <c r="U263" s="9" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="V263" s="20" t="inlineStr">
         <is>
@@ -24440,33 +24440,33 @@
       <c r="L264" s="32" t="n">
         <v>3968</v>
       </c>
-      <c r="M264" s="40" t="n">
+      <c r="M264" s="33" t="n">
         <v>3983</v>
       </c>
-      <c r="N264" s="40" t="n">
+      <c r="N264" s="33" t="n">
         <v>4003</v>
       </c>
-      <c r="O264" s="40" t="n">
+      <c r="O264" s="33" t="n">
         <v>4015.75</v>
       </c>
-      <c r="P264" s="41" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="Q264" s="8" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="R264" s="8" t="n"/>
-      <c r="S264" s="8" t="n"/>
-      <c r="T264" s="40" t="n"/>
-      <c r="U264" s="47" t="n"/>
-      <c r="V264" s="43" t="inlineStr">
+      <c r="P264" s="34" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q264" s="5" t="inlineStr">
+        <is>
+          <t>NO_FILL</t>
+        </is>
+      </c>
+      <c r="R264" s="5" t="n"/>
+      <c r="S264" s="5" t="n"/>
+      <c r="T264" s="33" t="n"/>
+      <c r="U264" s="35" t="n"/>
+      <c r="V264" s="36" t="inlineStr">
         <is>
           <t>1:1.6</t>
         </is>
       </c>
-      <c r="W264" s="48" t="n"/>
+      <c r="W264" s="37" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="31" t="inlineStr">
@@ -24517,33 +24517,33 @@
       <c r="L265" s="32" t="n">
         <v>3968</v>
       </c>
-      <c r="M265" s="40" t="n">
+      <c r="M265" s="33" t="n">
         <v>3983</v>
       </c>
-      <c r="N265" s="40" t="n">
+      <c r="N265" s="33" t="n">
         <v>4004</v>
       </c>
-      <c r="O265" s="40" t="n">
+      <c r="O265" s="33" t="n">
         <v>4016.75</v>
       </c>
-      <c r="P265" s="41" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="Q265" s="8" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="R265" s="8" t="n"/>
-      <c r="S265" s="8" t="n"/>
-      <c r="T265" s="40" t="n"/>
-      <c r="U265" s="47" t="n"/>
-      <c r="V265" s="43" t="inlineStr">
+      <c r="P265" s="34" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q265" s="5" t="inlineStr">
+        <is>
+          <t>NO_FILL</t>
+        </is>
+      </c>
+      <c r="R265" s="5" t="n"/>
+      <c r="S265" s="5" t="n"/>
+      <c r="T265" s="33" t="n"/>
+      <c r="U265" s="35" t="n"/>
+      <c r="V265" s="36" t="inlineStr">
         <is>
           <t>1:1.6</t>
         </is>
       </c>
-      <c r="W265" s="48" t="n"/>
+      <c r="W265" s="37" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="31" t="inlineStr">
@@ -24594,33 +24594,33 @@
       <c r="L266" s="32" t="n">
         <v>3968</v>
       </c>
-      <c r="M266" s="40" t="n">
+      <c r="M266" s="33" t="n">
         <v>3983</v>
       </c>
-      <c r="N266" s="40" t="n">
+      <c r="N266" s="33" t="n">
         <v>4005</v>
       </c>
-      <c r="O266" s="40" t="n">
+      <c r="O266" s="33" t="n">
         <v>4017.75</v>
       </c>
-      <c r="P266" s="41" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="Q266" s="8" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="R266" s="8" t="n"/>
-      <c r="S266" s="8" t="n"/>
-      <c r="T266" s="40" t="n"/>
-      <c r="U266" s="47" t="n"/>
-      <c r="V266" s="43" t="inlineStr">
+      <c r="P266" s="34" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q266" s="5" t="inlineStr">
+        <is>
+          <t>NO_FILL</t>
+        </is>
+      </c>
+      <c r="R266" s="5" t="n"/>
+      <c r="S266" s="5" t="n"/>
+      <c r="T266" s="33" t="n"/>
+      <c r="U266" s="35" t="n"/>
+      <c r="V266" s="36" t="inlineStr">
         <is>
           <t>1:1.7</t>
         </is>
       </c>
-      <c r="W266" s="48" t="n"/>
+      <c r="W266" s="37" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="31" t="inlineStr">
@@ -24681,7 +24681,7 @@
         <v>3973.1</v>
       </c>
       <c r="P267" s="41" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q267" s="8" t="inlineStr">
         <is>
@@ -24758,7 +24758,7 @@
         <v>3972.171428571428</v>
       </c>
       <c r="P268" s="41" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q268" s="8" t="inlineStr">
         <is>
@@ -24835,7 +24835,7 @@
         <v>3971.242857142857</v>
       </c>
       <c r="P269" s="41" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q269" s="8" t="inlineStr">
         <is>
@@ -24912,7 +24912,7 @@
         <v>3970.314285714286</v>
       </c>
       <c r="P270" s="41" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q270" s="8" t="inlineStr">
         <is>
@@ -24989,7 +24989,7 @@
         <v>3969.385714285714</v>
       </c>
       <c r="P271" s="41" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q271" s="8" t="inlineStr">
         <is>
@@ -25066,7 +25066,7 @@
         <v>3968.457142857143</v>
       </c>
       <c r="P272" s="41" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q272" s="8" t="inlineStr">
         <is>
@@ -25143,7 +25143,7 @@
         <v>3967.528571428571</v>
       </c>
       <c r="P273" s="41" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q273" s="8" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>3966.6</v>
       </c>
       <c r="P274" s="41" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q274" s="8" t="inlineStr">
         <is>
@@ -25287,33 +25287,49 @@
       <c r="L275" s="32" t="n">
         <v>4021</v>
       </c>
-      <c r="M275" s="40" t="n">
+      <c r="M275" s="38" t="n">
         <v>4006</v>
       </c>
-      <c r="N275" s="40" t="n">
-        <v>3991</v>
-      </c>
-      <c r="O275" s="40" t="n">
+      <c r="N275" s="38" t="n">
+        <v>3990.95</v>
+      </c>
+      <c r="O275" s="38" t="n">
         <v>3979.1</v>
       </c>
-      <c r="P275" s="41" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="Q275" s="8" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="R275" s="8" t="n"/>
-      <c r="S275" s="8" t="n"/>
-      <c r="T275" s="40" t="n"/>
-      <c r="U275" s="47" t="n"/>
-      <c r="V275" s="43" t="inlineStr">
+      <c r="P275" s="17" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q275" s="6" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="R275" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-25 12:52</t>
+        </is>
+      </c>
+      <c r="S275" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:16</t>
+        </is>
+      </c>
+      <c r="T275" s="38" t="n">
+        <v>3979.1</v>
+      </c>
+      <c r="U275" s="15" t="n">
+        <v>-11.84999999999991</v>
+      </c>
+      <c r="V275" s="13" t="inlineStr">
         <is>
           <t>1:1.3</t>
         </is>
       </c>
-      <c r="W275" s="48" t="n"/>
+      <c r="W275" s="14" t="inlineStr">
+        <is>
+          <t>-1.0R</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="31" t="inlineStr">
@@ -25364,33 +25380,49 @@
       <c r="L276" s="32" t="n">
         <v>4021</v>
       </c>
-      <c r="M276" s="40" t="n">
+      <c r="M276" s="38" t="n">
         <v>4006</v>
       </c>
-      <c r="N276" s="40" t="n">
-        <v>3990.071428571428</v>
-      </c>
-      <c r="O276" s="40" t="n">
+      <c r="N276" s="38" t="n">
+        <v>3990.05</v>
+      </c>
+      <c r="O276" s="38" t="n">
         <v>3978.171428571428</v>
       </c>
-      <c r="P276" s="41" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="Q276" s="8" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="R276" s="8" t="n"/>
-      <c r="S276" s="8" t="n"/>
-      <c r="T276" s="40" t="n"/>
-      <c r="U276" s="47" t="n"/>
-      <c r="V276" s="43" t="inlineStr">
+      <c r="P276" s="17" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q276" s="6" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="R276" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-25 12:53</t>
+        </is>
+      </c>
+      <c r="S276" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:17</t>
+        </is>
+      </c>
+      <c r="T276" s="38" t="n">
+        <v>3978.17</v>
+      </c>
+      <c r="U276" s="15" t="n">
+        <v>-11.88000000000011</v>
+      </c>
+      <c r="V276" s="13" t="inlineStr">
         <is>
           <t>1:1.3</t>
         </is>
       </c>
-      <c r="W276" s="48" t="n"/>
+      <c r="W276" s="14" t="inlineStr">
+        <is>
+          <t>-1.0R</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="31" t="inlineStr">
@@ -25441,33 +25473,49 @@
       <c r="L277" s="32" t="n">
         <v>4021</v>
       </c>
-      <c r="M277" s="40" t="n">
+      <c r="M277" s="38" t="n">
         <v>4006</v>
       </c>
-      <c r="N277" s="40" t="n">
-        <v>3989.142857142857</v>
-      </c>
-      <c r="O277" s="40" t="n">
+      <c r="N277" s="38" t="n">
+        <v>3989.06</v>
+      </c>
+      <c r="O277" s="38" t="n">
         <v>3977.242857142857</v>
       </c>
-      <c r="P277" s="41" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="Q277" s="8" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="R277" s="8" t="n"/>
-      <c r="S277" s="8" t="n"/>
-      <c r="T277" s="40" t="n"/>
-      <c r="U277" s="47" t="n"/>
-      <c r="V277" s="43" t="inlineStr">
+      <c r="P277" s="17" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q277" s="6" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="R277" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-25 12:59</t>
+        </is>
+      </c>
+      <c r="S277" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:17</t>
+        </is>
+      </c>
+      <c r="T277" s="38" t="n">
+        <v>3977.24</v>
+      </c>
+      <c r="U277" s="15" t="n">
+        <v>-11.82000000000016</v>
+      </c>
+      <c r="V277" s="13" t="inlineStr">
         <is>
           <t>1:1.4</t>
         </is>
       </c>
-      <c r="W277" s="48" t="n"/>
+      <c r="W277" s="14" t="inlineStr">
+        <is>
+          <t>-1.0R</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="31" t="inlineStr">
@@ -25518,33 +25566,49 @@
       <c r="L278" s="32" t="n">
         <v>4021</v>
       </c>
-      <c r="M278" s="40" t="n">
+      <c r="M278" s="38" t="n">
         <v>4006</v>
       </c>
-      <c r="N278" s="40" t="n">
-        <v>3988.214285714286</v>
-      </c>
-      <c r="O278" s="40" t="n">
+      <c r="N278" s="38" t="n">
+        <v>3988.19</v>
+      </c>
+      <c r="O278" s="38" t="n">
         <v>3976.314285714286</v>
       </c>
-      <c r="P278" s="41" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="Q278" s="8" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="R278" s="8" t="n"/>
-      <c r="S278" s="8" t="n"/>
-      <c r="T278" s="40" t="n"/>
-      <c r="U278" s="47" t="n"/>
-      <c r="V278" s="43" t="inlineStr">
+      <c r="P278" s="17" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q278" s="6" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="R278" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-25 12:59</t>
+        </is>
+      </c>
+      <c r="S278" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:17</t>
+        </is>
+      </c>
+      <c r="T278" s="38" t="n">
+        <v>3976.31</v>
+      </c>
+      <c r="U278" s="15" t="n">
+        <v>-11.88000000000011</v>
+      </c>
+      <c r="V278" s="13" t="inlineStr">
         <is>
           <t>1:1.5</t>
         </is>
       </c>
-      <c r="W278" s="48" t="n"/>
+      <c r="W278" s="14" t="inlineStr">
+        <is>
+          <t>-1.0R</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="31" t="inlineStr">
@@ -25595,33 +25659,49 @@
       <c r="L279" s="32" t="n">
         <v>4021</v>
       </c>
-      <c r="M279" s="40" t="n">
+      <c r="M279" s="38" t="n">
         <v>4006</v>
       </c>
-      <c r="N279" s="40" t="n">
-        <v>3987.285714285714</v>
-      </c>
-      <c r="O279" s="40" t="n">
+      <c r="N279" s="38" t="n">
+        <v>3987.28</v>
+      </c>
+      <c r="O279" s="38" t="n">
         <v>3975.385714285714</v>
       </c>
-      <c r="P279" s="41" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="Q279" s="8" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="R279" s="8" t="n"/>
-      <c r="S279" s="8" t="n"/>
-      <c r="T279" s="40" t="n"/>
-      <c r="U279" s="47" t="n"/>
-      <c r="V279" s="43" t="inlineStr">
+      <c r="P279" s="17" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q279" s="6" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="R279" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:03</t>
+        </is>
+      </c>
+      <c r="S279" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:35</t>
+        </is>
+      </c>
+      <c r="T279" s="38" t="n">
+        <v>3975.39</v>
+      </c>
+      <c r="U279" s="15" t="n">
+        <v>-11.89000000000033</v>
+      </c>
+      <c r="V279" s="13" t="inlineStr">
         <is>
           <t>1:1.6</t>
         </is>
       </c>
-      <c r="W279" s="48" t="n"/>
+      <c r="W279" s="14" t="inlineStr">
+        <is>
+          <t>-1.0R</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="31" t="inlineStr">
@@ -25672,33 +25752,49 @@
       <c r="L280" s="32" t="n">
         <v>4021</v>
       </c>
-      <c r="M280" s="40" t="n">
+      <c r="M280" s="38" t="n">
         <v>4006</v>
       </c>
-      <c r="N280" s="40" t="n">
-        <v>3986.357142857143</v>
-      </c>
-      <c r="O280" s="40" t="n">
+      <c r="N280" s="38" t="n">
+        <v>3986.35</v>
+      </c>
+      <c r="O280" s="38" t="n">
         <v>3974.457142857143</v>
       </c>
-      <c r="P280" s="41" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="Q280" s="8" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="R280" s="8" t="n"/>
-      <c r="S280" s="8" t="n"/>
-      <c r="T280" s="40" t="n"/>
-      <c r="U280" s="47" t="n"/>
-      <c r="V280" s="43" t="inlineStr">
+      <c r="P280" s="17" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q280" s="6" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="R280" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-25 13:03</t>
+        </is>
+      </c>
+      <c r="S280" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-25 14:36</t>
+        </is>
+      </c>
+      <c r="T280" s="38" t="n">
+        <v>3974.46</v>
+      </c>
+      <c r="U280" s="15" t="n">
+        <v>-11.88999999999987</v>
+      </c>
+      <c r="V280" s="13" t="inlineStr">
         <is>
           <t>1:1.7</t>
         </is>
       </c>
-      <c r="W280" s="48" t="n"/>
+      <c r="W280" s="14" t="inlineStr">
+        <is>
+          <t>-1.0R</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="31" t="inlineStr">
@@ -25759,7 +25855,7 @@
         <v>3973.528571428571</v>
       </c>
       <c r="P281" s="41" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q281" s="8" t="inlineStr">
         <is>
@@ -25836,7 +25932,7 @@
         <v>3972.6</v>
       </c>
       <c r="P282" s="41" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="Q282" s="8" t="inlineStr">
         <is>

--- a/reports/V116_202606.xlsx
+++ b/reports/V116_202606.xlsx
@@ -12,8 +12,8 @@
     <sheet name="Per-Entry Detail" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Breakdown'!$A$1:$S$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Per-Entry Detail'!$A$2:$W$282</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Breakdown'!$A$1:$S$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Per-Entry Detail'!$A$2:$W$303</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -610,9 +610,9 @@
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
     <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -772,7 +772,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-25 18:09:00</t>
+          <t>2026-06-26 11:21:00</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>$14,028.12</t>
+          <t>$13,922.34</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>$2,028.12</t>
+          <t>$1,922.34</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>$2,014.08</t>
+          <t>$1,906.32</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>$14.04</t>
+          <t>$16.02</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>+16.90%</t>
+          <t>+16.02%</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26">
@@ -874,7 +874,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>17 / 10</t>
+          <t>19 / 12</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>62.96%</t>
+          <t>61.29%</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>TICK 40 / M1 0</t>
+          <t>TICK 43 / M1 0</t>
         </is>
       </c>
     </row>
@@ -934,11 +934,11 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>36.2%</t>
         </is>
       </c>
     </row>
@@ -949,11 +949,11 @@
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>28.9%</t>
         </is>
       </c>
     </row>
@@ -964,11 +964,11 @@
         </is>
       </c>
       <c r="B34" s="7" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>28.2%</t>
         </is>
       </c>
     </row>
@@ -983,7 +983,7 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>2.0%</t>
         </is>
       </c>
     </row>
@@ -994,11 +994,11 @@
         </is>
       </c>
       <c r="B36" s="8" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>4.7%</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>280</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38"/>
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>164</v>
+        <v>178</v>
       </c>
     </row>
     <row r="41">
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>96</v>
+        <v>109</v>
       </c>
     </row>
     <row r="42">
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="43">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>77</v>
+        <v>89</v>
       </c>
     </row>
     <row r="44">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1:0.37</t>
+          <t>1:0.29</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1:1.62</t>
+          <t>1:1.60</t>
         </is>
       </c>
     </row>
@@ -1183,41 +1183,41 @@
         </is>
       </c>
       <c r="C50" s="7" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D50" s="7" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E50" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F50" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="F50" s="7" t="n">
-        <v>9</v>
-      </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="H50" s="9" t="n">
-        <v>2014.080000000054</v>
+        <v>1906.320000000053</v>
       </c>
       <c r="I50" s="9" t="n">
-        <v>14.04</v>
+        <v>16.02000000000001</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>4.679999999999999</v>
+        <v>5.339999999999998</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>2028.120000000054</v>
+        <v>1922.340000000054</v>
       </c>
       <c r="L50" s="11" t="inlineStr">
         <is>
-          <t>+16.90%</t>
+          <t>+16.02%</t>
         </is>
       </c>
       <c r="M50" s="12" t="n">
-        <v>14028.12000000005</v>
+        <v>13922.34000000005</v>
       </c>
     </row>
   </sheetData>
@@ -1239,7 +1239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S5"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="M2" s="15" t="n">
-        <v>-235.1699999999682</v>
+        <v>-235.739999999967</v>
       </c>
       <c r="N2" s="16" t="n">
         <v>4.949999999999999</v>
@@ -1413,7 +1413,7 @@
         <v>1.65</v>
       </c>
       <c r="P2" s="15" t="n">
-        <v>-230.2199999999683</v>
+        <v>-230.7899999999671</v>
       </c>
       <c r="Q2" s="18" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         </is>
       </c>
       <c r="R2" s="19" t="n">
-        <v>11769.78000000003</v>
+        <v>11769.21000000003</v>
       </c>
       <c r="S2" s="18" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="M3" s="9" t="n">
-        <v>1483.740000000022</v>
+        <v>1483.710000000021</v>
       </c>
       <c r="N3" s="9" t="n">
         <v>3.96</v>
@@ -1482,7 +1482,7 @@
         <v>1.32</v>
       </c>
       <c r="P3" s="9" t="n">
-        <v>1487.700000000021</v>
+        <v>1487.670000000021</v>
       </c>
       <c r="Q3" s="11" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="R3" s="12" t="n">
-        <v>13257.48000000005</v>
+        <v>13256.88000000005</v>
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="R4" s="19" t="n">
-        <v>12854.73000000005</v>
+        <v>12854.13000000005</v>
       </c>
       <c r="S4" s="18" t="inlineStr">
         <is>
@@ -1577,25 +1577,25 @@
         <v>12</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J5" s="7" t="n">
         <v>84</v>
@@ -1607,28 +1607,28 @@
       </c>
       <c r="L5" s="21" t="inlineStr">
         <is>
-          <t>1:0.80</t>
+          <t>1:0.66</t>
         </is>
       </c>
       <c r="M5" s="9" t="n">
-        <v>1169.7</v>
+        <v>1318.289999999998</v>
       </c>
       <c r="N5" s="9" t="n">
-        <v>3.69</v>
+        <v>5.039999999999999</v>
       </c>
       <c r="O5" s="10" t="n">
-        <v>1.23</v>
+        <v>1.68</v>
       </c>
       <c r="P5" s="9" t="n">
-        <v>1173.39</v>
+        <v>1323.329999999998</v>
       </c>
       <c r="Q5" s="11" t="inlineStr">
         <is>
-          <t>+9.13%</t>
+          <t>+10.29%</t>
         </is>
       </c>
       <c r="R5" s="12" t="n">
-        <v>14028.12000000005</v>
+        <v>14177.46000000005</v>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
@@ -1636,8 +1636,77 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="K6" s="13" t="inlineStr">
+        <is>
+          <t>1:1.5</t>
+        </is>
+      </c>
+      <c r="L6" s="14" t="inlineStr">
+        <is>
+          <t>-1.0R</t>
+        </is>
+      </c>
+      <c r="M6" s="15" t="n">
+        <v>-255.7499999999986</v>
+      </c>
+      <c r="N6" s="16" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="O6" s="17" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="P6" s="15" t="n">
+        <v>-255.1199999999986</v>
+      </c>
+      <c r="Q6" s="18" t="inlineStr">
+        <is>
+          <t>-1.80%</t>
+        </is>
+      </c>
+      <c r="R6" s="19" t="n">
+        <v>13922.34000000005</v>
+      </c>
+      <c r="S6" s="18" t="inlineStr">
+        <is>
+          <t>-1.80%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S5"/>
+  <autoFilter ref="A1:S6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1648,7 +1717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W282"/>
+  <dimension ref="A1:W303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2515,7 +2584,7 @@
         <v>4166</v>
       </c>
       <c r="N11" s="38" t="n">
-        <v>4185.24</v>
+        <v>4185.2</v>
       </c>
       <c r="O11" s="38" t="n">
         <v>4197.916666666667</v>
@@ -2542,7 +2611,7 @@
         <v>4197.92</v>
       </c>
       <c r="U11" s="15" t="n">
-        <v>-38.04000000000087</v>
+        <v>-38.16000000000076</v>
       </c>
       <c r="V11" s="13" t="inlineStr">
         <is>
@@ -5995,7 +6064,7 @@
         <v>4208</v>
       </c>
       <c r="N51" s="40" t="n">
-        <v>4182.35</v>
+        <v>4182.48</v>
       </c>
       <c r="O51" s="40" t="n">
         <v>4168.9</v>
@@ -6022,7 +6091,7 @@
         <v>4177.71</v>
       </c>
       <c r="U51" s="42" t="n">
-        <v>-13.92000000000098</v>
+        <v>-14.30999999999858</v>
       </c>
       <c r="V51" s="43" t="inlineStr">
         <is>
@@ -6031,7 +6100,7 @@
       </c>
       <c r="W51" s="44" t="inlineStr">
         <is>
-          <t>-0.3R</t>
+          <t>-0.4R</t>
         </is>
       </c>
     </row>
@@ -8134,7 +8203,7 @@
         <v>4205</v>
       </c>
       <c r="N74" s="38" t="n">
-        <v>4185.9</v>
+        <v>4185.92</v>
       </c>
       <c r="O74" s="38" t="n">
         <v>4174.016666666667</v>
@@ -8161,7 +8230,7 @@
         <v>4174.02</v>
       </c>
       <c r="U74" s="15" t="n">
-        <v>-35.6399999999976</v>
+        <v>-35.6999999999989</v>
       </c>
       <c r="V74" s="13" t="inlineStr">
         <is>
@@ -14026,7 +14095,7 @@
         <v>4130</v>
       </c>
       <c r="N142" s="39" t="n">
-        <v>4105.49</v>
+        <v>4105.5</v>
       </c>
       <c r="O142" s="39" t="n">
         <v>4093.6</v>
@@ -14053,7 +14122,7 @@
         <v>4130</v>
       </c>
       <c r="U142" s="9" t="n">
-        <v>73.53000000000065</v>
+        <v>73.5</v>
       </c>
       <c r="V142" s="20" t="inlineStr">
         <is>
@@ -18815,7 +18884,7 @@
         <v>4000</v>
       </c>
       <c r="N199" s="38" t="n">
-        <v>3985</v>
+        <v>3984.88</v>
       </c>
       <c r="O199" s="38" t="n">
         <v>3973.1</v>
@@ -18830,7 +18899,7 @@
       </c>
       <c r="R199" s="6" t="inlineStr">
         <is>
-          <t>2026-06-25 10:10</t>
+          <t>2026-06-25 08:38</t>
         </is>
       </c>
       <c r="S199" s="6" t="inlineStr">
@@ -18842,7 +18911,7 @@
         <v>3973.1</v>
       </c>
       <c r="U199" s="15" t="n">
-        <v>-35.70000000000027</v>
+        <v>-35.3400000000006</v>
       </c>
       <c r="V199" s="13" t="inlineStr">
         <is>
@@ -18908,7 +18977,7 @@
         <v>4000</v>
       </c>
       <c r="N200" s="38" t="n">
-        <v>3983.83</v>
+        <v>3983.88</v>
       </c>
       <c r="O200" s="38" t="n">
         <v>3972.016666666666</v>
@@ -18923,7 +18992,7 @@
       </c>
       <c r="R200" s="6" t="inlineStr">
         <is>
-          <t>2026-06-25 10:10</t>
+          <t>2026-06-25 08:41</t>
         </is>
       </c>
       <c r="S200" s="6" t="inlineStr">
@@ -18935,7 +19004,7 @@
         <v>3972.02</v>
       </c>
       <c r="U200" s="15" t="n">
-        <v>-35.42999999999984</v>
+        <v>-35.58000000000037</v>
       </c>
       <c r="V200" s="13" t="inlineStr">
         <is>
@@ -19001,7 +19070,7 @@
         <v>4000</v>
       </c>
       <c r="N201" s="39" t="n">
-        <v>3982.78</v>
+        <v>3982.75</v>
       </c>
       <c r="O201" s="39" t="n">
         <v>3970.933333333333</v>
@@ -19016,7 +19085,7 @@
       </c>
       <c r="R201" s="7" t="inlineStr">
         <is>
-          <t>2026-06-25 10:12</t>
+          <t>2026-06-25 08:42</t>
         </is>
       </c>
       <c r="S201" s="7" t="inlineStr">
@@ -19028,7 +19097,7 @@
         <v>4000</v>
       </c>
       <c r="U201" s="9" t="n">
-        <v>51.65999999999939</v>
+        <v>51.74999999999999</v>
       </c>
       <c r="V201" s="20" t="inlineStr">
         <is>
@@ -19037,7 +19106,7 @@
       </c>
       <c r="W201" s="21" t="inlineStr">
         <is>
-          <t>1:1.45</t>
+          <t>1:1.46</t>
         </is>
       </c>
     </row>
@@ -19094,7 +19163,7 @@
         <v>4000</v>
       </c>
       <c r="N202" s="39" t="n">
-        <v>3981.68</v>
+        <v>3981.71</v>
       </c>
       <c r="O202" s="39" t="n">
         <v>3969.85</v>
@@ -19109,7 +19178,7 @@
       </c>
       <c r="R202" s="7" t="inlineStr">
         <is>
-          <t>2026-06-25 10:12</t>
+          <t>2026-06-25 08:45</t>
         </is>
       </c>
       <c r="S202" s="7" t="inlineStr">
@@ -19121,7 +19190,7 @@
         <v>4000</v>
       </c>
       <c r="U202" s="9" t="n">
-        <v>54.96000000000048</v>
+        <v>54.86999999999988</v>
       </c>
       <c r="V202" s="20" t="inlineStr">
         <is>
@@ -19130,7 +19199,7 @@
       </c>
       <c r="W202" s="21" t="inlineStr">
         <is>
-          <t>1:1.55</t>
+          <t>1:1.54</t>
         </is>
       </c>
     </row>
@@ -19187,7 +19256,7 @@
         <v>4000</v>
       </c>
       <c r="N203" s="39" t="n">
-        <v>3980.67</v>
+        <v>3980.56</v>
       </c>
       <c r="O203" s="39" t="n">
         <v>3968.766666666666</v>
@@ -19202,7 +19271,7 @@
       </c>
       <c r="R203" s="7" t="inlineStr">
         <is>
-          <t>2026-06-25 10:13</t>
+          <t>2026-06-25 08:46</t>
         </is>
       </c>
       <c r="S203" s="7" t="inlineStr">
@@ -19214,7 +19283,7 @@
         <v>4000</v>
       </c>
       <c r="U203" s="9" t="n">
-        <v>57.98999999999977</v>
+        <v>58.32000000000016</v>
       </c>
       <c r="V203" s="20" t="inlineStr">
         <is>
@@ -19223,7 +19292,7 @@
       </c>
       <c r="W203" s="21" t="inlineStr">
         <is>
-          <t>1:1.62</t>
+          <t>1:1.65</t>
         </is>
       </c>
     </row>
@@ -19280,7 +19349,7 @@
         <v>4000</v>
       </c>
       <c r="N204" s="39" t="n">
-        <v>3979.47</v>
+        <v>3979.55</v>
       </c>
       <c r="O204" s="39" t="n">
         <v>3967.683333333333</v>
@@ -19295,7 +19364,7 @@
       </c>
       <c r="R204" s="7" t="inlineStr">
         <is>
-          <t>2026-06-25 10:13</t>
+          <t>2026-06-25 09:15</t>
         </is>
       </c>
       <c r="S204" s="7" t="inlineStr">
@@ -19307,7 +19376,7 @@
         <v>4000</v>
       </c>
       <c r="U204" s="9" t="n">
-        <v>61.5900000000006</v>
+        <v>61.34999999999945</v>
       </c>
       <c r="V204" s="20" t="inlineStr">
         <is>
@@ -19316,7 +19385,7 @@
       </c>
       <c r="W204" s="21" t="inlineStr">
         <is>
-          <t>1:1.74</t>
+          <t>1:1.72</t>
         </is>
       </c>
     </row>
@@ -19373,7 +19442,7 @@
         <v>4000</v>
       </c>
       <c r="N205" s="39" t="n">
-        <v>3978.5</v>
+        <v>3978.38</v>
       </c>
       <c r="O205" s="39" t="n">
         <v>3966.6</v>
@@ -19388,7 +19457,7 @@
       </c>
       <c r="R205" s="7" t="inlineStr">
         <is>
-          <t>2026-06-25 10:15</t>
+          <t>2026-06-25 09:15</t>
         </is>
       </c>
       <c r="S205" s="7" t="inlineStr">
@@ -19400,7 +19469,7 @@
         <v>4000</v>
       </c>
       <c r="U205" s="9" t="n">
-        <v>64.5</v>
+        <v>64.85999999999967</v>
       </c>
       <c r="V205" s="20" t="inlineStr">
         <is>
@@ -19409,7 +19478,7 @@
       </c>
       <c r="W205" s="21" t="inlineStr">
         <is>
-          <t>1:1.81</t>
+          <t>1:1.84</t>
         </is>
       </c>
     </row>
@@ -22016,7 +22085,7 @@
         <v>4000</v>
       </c>
       <c r="N236" s="39" t="n">
-        <v>3982.79</v>
+        <v>3982.82</v>
       </c>
       <c r="O236" s="39" t="n">
         <v>3970.933333333333</v>
@@ -22043,7 +22112,7 @@
         <v>4000</v>
       </c>
       <c r="U236" s="9" t="n">
-        <v>51.63000000000011</v>
+        <v>51.53999999999951</v>
       </c>
       <c r="V236" s="20" t="inlineStr">
         <is>
@@ -23225,7 +23294,7 @@
         <v>4002</v>
       </c>
       <c r="N249" s="38" t="n">
-        <v>4018.21</v>
+        <v>4018.22</v>
       </c>
       <c r="O249" s="38" t="n">
         <v>4030.916666666667</v>
@@ -23252,7 +23321,7 @@
         <v>4030.92</v>
       </c>
       <c r="U249" s="15" t="n">
-        <v>-38.13000000000011</v>
+        <v>-38.10000000000082</v>
       </c>
       <c r="V249" s="13" t="inlineStr">
         <is>
@@ -24337,33 +24406,33 @@
       <c r="L261" s="32" t="n">
         <v>4035</v>
       </c>
-      <c r="M261" s="40" t="n">
+      <c r="M261" s="33" t="n">
         <v>4020</v>
       </c>
-      <c r="N261" s="40" t="n">
+      <c r="N261" s="33" t="n">
         <v>3998.5</v>
       </c>
-      <c r="O261" s="40" t="n">
+      <c r="O261" s="33" t="n">
         <v>3986.6</v>
       </c>
-      <c r="P261" s="41" t="n">
+      <c r="P261" s="34" t="n">
         <v>0.04</v>
       </c>
-      <c r="Q261" s="8" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="R261" s="8" t="n"/>
-      <c r="S261" s="8" t="n"/>
-      <c r="T261" s="40" t="n"/>
-      <c r="U261" s="47" t="n"/>
-      <c r="V261" s="43" t="inlineStr">
+      <c r="Q261" s="5" t="inlineStr">
+        <is>
+          <t>NO_FILL</t>
+        </is>
+      </c>
+      <c r="R261" s="5" t="n"/>
+      <c r="S261" s="5" t="n"/>
+      <c r="T261" s="33" t="n"/>
+      <c r="U261" s="35" t="n"/>
+      <c r="V261" s="36" t="inlineStr">
         <is>
           <t>1:1.8</t>
         </is>
       </c>
-      <c r="W261" s="48" t="n"/>
+      <c r="W261" s="37" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="31" t="inlineStr">
@@ -24600,33 +24669,49 @@
       <c r="L264" s="32" t="n">
         <v>3985</v>
       </c>
-      <c r="M264" s="40" t="n">
+      <c r="M264" s="38" t="n">
         <v>4000</v>
       </c>
-      <c r="N264" s="40" t="n">
-        <v>4017.333333333333</v>
-      </c>
-      <c r="O264" s="40" t="n">
+      <c r="N264" s="38" t="n">
+        <v>4017.36</v>
+      </c>
+      <c r="O264" s="38" t="n">
         <v>4030.083333333333</v>
       </c>
-      <c r="P264" s="41" t="n">
+      <c r="P264" s="17" t="n">
         <v>0.03</v>
       </c>
-      <c r="Q264" s="8" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="R264" s="8" t="n"/>
-      <c r="S264" s="8" t="n"/>
-      <c r="T264" s="40" t="n"/>
-      <c r="U264" s="47" t="n"/>
-      <c r="V264" s="43" t="inlineStr">
+      <c r="Q264" s="6" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="R264" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-25 17:05</t>
+        </is>
+      </c>
+      <c r="S264" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-25 18:22</t>
+        </is>
+      </c>
+      <c r="T264" s="38" t="n">
+        <v>4030.08</v>
+      </c>
+      <c r="U264" s="15" t="n">
+        <v>-38.1599999999994</v>
+      </c>
+      <c r="V264" s="13" t="inlineStr">
         <is>
           <t>1:1.4</t>
         </is>
       </c>
-      <c r="W264" s="48" t="n"/>
+      <c r="W264" s="14" t="inlineStr">
+        <is>
+          <t>-1.0R</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="31" t="inlineStr">
@@ -24677,33 +24762,49 @@
       <c r="L265" s="32" t="n">
         <v>3985</v>
       </c>
-      <c r="M265" s="40" t="n">
+      <c r="M265" s="38" t="n">
         <v>4000</v>
       </c>
-      <c r="N265" s="40" t="n">
+      <c r="N265" s="38" t="n">
         <v>4018.5</v>
       </c>
-      <c r="O265" s="40" t="n">
+      <c r="O265" s="38" t="n">
         <v>4031.25</v>
       </c>
-      <c r="P265" s="41" t="n">
+      <c r="P265" s="17" t="n">
         <v>0.03</v>
       </c>
-      <c r="Q265" s="8" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="R265" s="8" t="n"/>
-      <c r="S265" s="8" t="n"/>
-      <c r="T265" s="40" t="n"/>
-      <c r="U265" s="47" t="n"/>
-      <c r="V265" s="43" t="inlineStr">
+      <c r="Q265" s="6" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="R265" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-25 17:05</t>
+        </is>
+      </c>
+      <c r="S265" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-25 18:22</t>
+        </is>
+      </c>
+      <c r="T265" s="38" t="n">
+        <v>4031.25</v>
+      </c>
+      <c r="U265" s="15" t="n">
+        <v>-38.25</v>
+      </c>
+      <c r="V265" s="13" t="inlineStr">
         <is>
           <t>1:1.5</t>
         </is>
       </c>
-      <c r="W265" s="48" t="n"/>
+      <c r="W265" s="14" t="inlineStr">
+        <is>
+          <t>-1.0R</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="31" t="inlineStr">
@@ -24754,33 +24855,49 @@
       <c r="L266" s="32" t="n">
         <v>3985</v>
       </c>
-      <c r="M266" s="40" t="n">
+      <c r="M266" s="38" t="n">
         <v>4000</v>
       </c>
-      <c r="N266" s="40" t="n">
-        <v>4019.666666666667</v>
-      </c>
-      <c r="O266" s="40" t="n">
+      <c r="N266" s="38" t="n">
+        <v>4019.68</v>
+      </c>
+      <c r="O266" s="38" t="n">
         <v>4032.416666666667</v>
       </c>
-      <c r="P266" s="41" t="n">
+      <c r="P266" s="17" t="n">
         <v>0.03</v>
       </c>
-      <c r="Q266" s="8" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="R266" s="8" t="n"/>
-      <c r="S266" s="8" t="n"/>
-      <c r="T266" s="40" t="n"/>
-      <c r="U266" s="47" t="n"/>
-      <c r="V266" s="43" t="inlineStr">
+      <c r="Q266" s="6" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="R266" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-25 17:06</t>
+        </is>
+      </c>
+      <c r="S266" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-25 18:22</t>
+        </is>
+      </c>
+      <c r="T266" s="38" t="n">
+        <v>4032.42</v>
+      </c>
+      <c r="U266" s="15" t="n">
+        <v>-38.22000000000071</v>
+      </c>
+      <c r="V266" s="13" t="inlineStr">
         <is>
           <t>1:1.5</t>
         </is>
       </c>
-      <c r="W266" s="48" t="n"/>
+      <c r="W266" s="14" t="inlineStr">
+        <is>
+          <t>-1.0R</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="31" t="inlineStr">
@@ -24831,33 +24948,49 @@
       <c r="L267" s="32" t="n">
         <v>3985</v>
       </c>
-      <c r="M267" s="40" t="n">
+      <c r="M267" s="38" t="n">
         <v>4000</v>
       </c>
-      <c r="N267" s="40" t="n">
-        <v>4020.833333333333</v>
-      </c>
-      <c r="O267" s="40" t="n">
+      <c r="N267" s="38" t="n">
+        <v>4021.59</v>
+      </c>
+      <c r="O267" s="38" t="n">
         <v>4033.583333333333</v>
       </c>
-      <c r="P267" s="41" t="n">
+      <c r="P267" s="17" t="n">
         <v>0.03</v>
       </c>
-      <c r="Q267" s="8" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="R267" s="8" t="n"/>
-      <c r="S267" s="8" t="n"/>
-      <c r="T267" s="40" t="n"/>
-      <c r="U267" s="47" t="n"/>
-      <c r="V267" s="43" t="inlineStr">
+      <c r="Q267" s="6" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="R267" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-25 17:06</t>
+        </is>
+      </c>
+      <c r="S267" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-25 18:22</t>
+        </is>
+      </c>
+      <c r="T267" s="38" t="n">
+        <v>4033.58</v>
+      </c>
+      <c r="U267" s="15" t="n">
+        <v>-35.96999999999934</v>
+      </c>
+      <c r="V267" s="13" t="inlineStr">
         <is>
           <t>1:1.6</t>
         </is>
       </c>
-      <c r="W267" s="48" t="n"/>
+      <c r="W267" s="14" t="inlineStr">
+        <is>
+          <t>-1.0R</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="31" t="inlineStr">
@@ -24908,33 +25041,49 @@
       <c r="L268" s="32" t="n">
         <v>3985</v>
       </c>
-      <c r="M268" s="40" t="n">
+      <c r="M268" s="38" t="n">
         <v>4000</v>
       </c>
-      <c r="N268" s="40" t="n">
-        <v>4022</v>
-      </c>
-      <c r="O268" s="40" t="n">
+      <c r="N268" s="38" t="n">
+        <v>4022.03</v>
+      </c>
+      <c r="O268" s="38" t="n">
         <v>4034.75</v>
       </c>
-      <c r="P268" s="41" t="n">
+      <c r="P268" s="17" t="n">
         <v>0.03</v>
       </c>
-      <c r="Q268" s="8" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="R268" s="8" t="n"/>
-      <c r="S268" s="8" t="n"/>
-      <c r="T268" s="40" t="n"/>
-      <c r="U268" s="47" t="n"/>
-      <c r="V268" s="43" t="inlineStr">
+      <c r="Q268" s="6" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="R268" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-25 17:21</t>
+        </is>
+      </c>
+      <c r="S268" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-25 18:22</t>
+        </is>
+      </c>
+      <c r="T268" s="38" t="n">
+        <v>4034.75</v>
+      </c>
+      <c r="U268" s="15" t="n">
+        <v>-38.1599999999994</v>
+      </c>
+      <c r="V268" s="13" t="inlineStr">
         <is>
           <t>1:1.7</t>
         </is>
       </c>
-      <c r="W268" s="48" t="n"/>
+      <c r="W268" s="14" t="inlineStr">
+        <is>
+          <t>-1.0R</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="31" t="inlineStr">
@@ -24985,33 +25134,49 @@
       <c r="L269" s="32" t="n">
         <v>4013</v>
       </c>
-      <c r="M269" s="40" t="n">
+      <c r="M269" s="39" t="n">
         <v>4028</v>
       </c>
-      <c r="N269" s="40" t="n">
-        <v>4043</v>
-      </c>
-      <c r="O269" s="40" t="n">
+      <c r="N269" s="39" t="n">
+        <v>4043.04</v>
+      </c>
+      <c r="O269" s="39" t="n">
         <v>4055.75</v>
       </c>
-      <c r="P269" s="41" t="n">
+      <c r="P269" s="10" t="n">
         <v>0.03</v>
       </c>
-      <c r="Q269" s="8" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="R269" s="8" t="n"/>
-      <c r="S269" s="8" t="n"/>
-      <c r="T269" s="40" t="n"/>
-      <c r="U269" s="47" t="n"/>
-      <c r="V269" s="43" t="inlineStr">
+      <c r="Q269" s="7" t="inlineStr">
+        <is>
+          <t>TP2</t>
+        </is>
+      </c>
+      <c r="R269" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-25 19:17</t>
+        </is>
+      </c>
+      <c r="S269" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-25 19:45</t>
+        </is>
+      </c>
+      <c r="T269" s="39" t="n">
+        <v>4028</v>
+      </c>
+      <c r="U269" s="9" t="n">
+        <v>45.11999999999989</v>
+      </c>
+      <c r="V269" s="20" t="inlineStr">
         <is>
           <t>1:1.2</t>
         </is>
       </c>
-      <c r="W269" s="48" t="n"/>
+      <c r="W269" s="21" t="inlineStr">
+        <is>
+          <t>1:1.18</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="31" t="inlineStr">
@@ -25062,33 +25227,49 @@
       <c r="L270" s="32" t="n">
         <v>4013</v>
       </c>
-      <c r="M270" s="40" t="n">
+      <c r="M270" s="39" t="n">
         <v>4028</v>
       </c>
-      <c r="N270" s="40" t="n">
-        <v>4044.166666666667</v>
-      </c>
-      <c r="O270" s="40" t="n">
+      <c r="N270" s="39" t="n">
+        <v>4044.18</v>
+      </c>
+      <c r="O270" s="39" t="n">
         <v>4056.916666666667</v>
       </c>
-      <c r="P270" s="41" t="n">
+      <c r="P270" s="10" t="n">
         <v>0.03</v>
       </c>
-      <c r="Q270" s="8" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="R270" s="8" t="n"/>
-      <c r="S270" s="8" t="n"/>
-      <c r="T270" s="40" t="n"/>
-      <c r="U270" s="47" t="n"/>
-      <c r="V270" s="43" t="inlineStr">
+      <c r="Q270" s="7" t="inlineStr">
+        <is>
+          <t>TP2</t>
+        </is>
+      </c>
+      <c r="R270" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-25 19:17</t>
+        </is>
+      </c>
+      <c r="S270" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-25 19:45</t>
+        </is>
+      </c>
+      <c r="T270" s="39" t="n">
+        <v>4028</v>
+      </c>
+      <c r="U270" s="9" t="n">
+        <v>48.53999999999951</v>
+      </c>
+      <c r="V270" s="20" t="inlineStr">
         <is>
           <t>1:1.3</t>
         </is>
       </c>
-      <c r="W270" s="48" t="n"/>
+      <c r="W270" s="21" t="inlineStr">
+        <is>
+          <t>1:1.27</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="31" t="inlineStr">
@@ -25139,33 +25320,33 @@
       <c r="L271" s="32" t="n">
         <v>4013</v>
       </c>
-      <c r="M271" s="40" t="n">
+      <c r="M271" s="33" t="n">
         <v>4028</v>
       </c>
-      <c r="N271" s="40" t="n">
+      <c r="N271" s="33" t="n">
         <v>4045.333333333333</v>
       </c>
-      <c r="O271" s="40" t="n">
+      <c r="O271" s="33" t="n">
         <v>4058.083333333333</v>
       </c>
-      <c r="P271" s="41" t="n">
+      <c r="P271" s="34" t="n">
         <v>0.03</v>
       </c>
-      <c r="Q271" s="8" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="R271" s="8" t="n"/>
-      <c r="S271" s="8" t="n"/>
-      <c r="T271" s="40" t="n"/>
-      <c r="U271" s="47" t="n"/>
-      <c r="V271" s="43" t="inlineStr">
+      <c r="Q271" s="5" t="inlineStr">
+        <is>
+          <t>NO_FILL</t>
+        </is>
+      </c>
+      <c r="R271" s="5" t="n"/>
+      <c r="S271" s="5" t="n"/>
+      <c r="T271" s="33" t="n"/>
+      <c r="U271" s="35" t="n"/>
+      <c r="V271" s="36" t="inlineStr">
         <is>
           <t>1:1.4</t>
         </is>
       </c>
-      <c r="W271" s="48" t="n"/>
+      <c r="W271" s="37" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="31" t="inlineStr">
@@ -25216,33 +25397,33 @@
       <c r="L272" s="32" t="n">
         <v>4013</v>
       </c>
-      <c r="M272" s="40" t="n">
+      <c r="M272" s="33" t="n">
         <v>4028</v>
       </c>
-      <c r="N272" s="40" t="n">
+      <c r="N272" s="33" t="n">
         <v>4046.5</v>
       </c>
-      <c r="O272" s="40" t="n">
+      <c r="O272" s="33" t="n">
         <v>4059.25</v>
       </c>
-      <c r="P272" s="41" t="n">
+      <c r="P272" s="34" t="n">
         <v>0.03</v>
       </c>
-      <c r="Q272" s="8" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="R272" s="8" t="n"/>
-      <c r="S272" s="8" t="n"/>
-      <c r="T272" s="40" t="n"/>
-      <c r="U272" s="47" t="n"/>
-      <c r="V272" s="43" t="inlineStr">
+      <c r="Q272" s="5" t="inlineStr">
+        <is>
+          <t>NO_FILL</t>
+        </is>
+      </c>
+      <c r="R272" s="5" t="n"/>
+      <c r="S272" s="5" t="n"/>
+      <c r="T272" s="33" t="n"/>
+      <c r="U272" s="35" t="n"/>
+      <c r="V272" s="36" t="inlineStr">
         <is>
           <t>1:1.5</t>
         </is>
       </c>
-      <c r="W272" s="48" t="n"/>
+      <c r="W272" s="37" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="31" t="inlineStr">
@@ -25293,33 +25474,33 @@
       <c r="L273" s="32" t="n">
         <v>4013</v>
       </c>
-      <c r="M273" s="40" t="n">
+      <c r="M273" s="33" t="n">
         <v>4028</v>
       </c>
-      <c r="N273" s="40" t="n">
+      <c r="N273" s="33" t="n">
         <v>4047.666666666667</v>
       </c>
-      <c r="O273" s="40" t="n">
+      <c r="O273" s="33" t="n">
         <v>4060.416666666667</v>
       </c>
-      <c r="P273" s="41" t="n">
+      <c r="P273" s="34" t="n">
         <v>0.03</v>
       </c>
-      <c r="Q273" s="8" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="R273" s="8" t="n"/>
-      <c r="S273" s="8" t="n"/>
-      <c r="T273" s="40" t="n"/>
-      <c r="U273" s="47" t="n"/>
-      <c r="V273" s="43" t="inlineStr">
+      <c r="Q273" s="5" t="inlineStr">
+        <is>
+          <t>NO_FILL</t>
+        </is>
+      </c>
+      <c r="R273" s="5" t="n"/>
+      <c r="S273" s="5" t="n"/>
+      <c r="T273" s="33" t="n"/>
+      <c r="U273" s="35" t="n"/>
+      <c r="V273" s="36" t="inlineStr">
         <is>
           <t>1:1.5</t>
         </is>
       </c>
-      <c r="W273" s="48" t="n"/>
+      <c r="W273" s="37" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="31" t="inlineStr">
@@ -25370,33 +25551,33 @@
       <c r="L274" s="32" t="n">
         <v>4013</v>
       </c>
-      <c r="M274" s="40" t="n">
+      <c r="M274" s="33" t="n">
         <v>4028</v>
       </c>
-      <c r="N274" s="40" t="n">
+      <c r="N274" s="33" t="n">
         <v>4048.833333333333</v>
       </c>
-      <c r="O274" s="40" t="n">
+      <c r="O274" s="33" t="n">
         <v>4061.583333333333</v>
       </c>
-      <c r="P274" s="41" t="n">
+      <c r="P274" s="34" t="n">
         <v>0.03</v>
       </c>
-      <c r="Q274" s="8" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="R274" s="8" t="n"/>
-      <c r="S274" s="8" t="n"/>
-      <c r="T274" s="40" t="n"/>
-      <c r="U274" s="47" t="n"/>
-      <c r="V274" s="43" t="inlineStr">
+      <c r="Q274" s="5" t="inlineStr">
+        <is>
+          <t>NO_FILL</t>
+        </is>
+      </c>
+      <c r="R274" s="5" t="n"/>
+      <c r="S274" s="5" t="n"/>
+      <c r="T274" s="33" t="n"/>
+      <c r="U274" s="35" t="n"/>
+      <c r="V274" s="36" t="inlineStr">
         <is>
           <t>1:1.6</t>
         </is>
       </c>
-      <c r="W274" s="48" t="n"/>
+      <c r="W274" s="37" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="31" t="inlineStr">
@@ -25447,33 +25628,33 @@
       <c r="L275" s="32" t="n">
         <v>4013</v>
       </c>
-      <c r="M275" s="40" t="n">
+      <c r="M275" s="33" t="n">
         <v>4028</v>
       </c>
-      <c r="N275" s="40" t="n">
+      <c r="N275" s="33" t="n">
         <v>4050</v>
       </c>
-      <c r="O275" s="40" t="n">
+      <c r="O275" s="33" t="n">
         <v>4062.75</v>
       </c>
-      <c r="P275" s="41" t="n">
+      <c r="P275" s="34" t="n">
         <v>0.03</v>
       </c>
-      <c r="Q275" s="8" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="R275" s="8" t="n"/>
-      <c r="S275" s="8" t="n"/>
-      <c r="T275" s="40" t="n"/>
-      <c r="U275" s="47" t="n"/>
-      <c r="V275" s="43" t="inlineStr">
+      <c r="Q275" s="5" t="inlineStr">
+        <is>
+          <t>NO_FILL</t>
+        </is>
+      </c>
+      <c r="R275" s="5" t="n"/>
+      <c r="S275" s="5" t="n"/>
+      <c r="T275" s="33" t="n"/>
+      <c r="U275" s="35" t="n"/>
+      <c r="V275" s="36" t="inlineStr">
         <is>
           <t>1:1.7</t>
         </is>
       </c>
-      <c r="W275" s="48" t="n"/>
+      <c r="W275" s="37" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="31" t="inlineStr">
@@ -25524,33 +25705,33 @@
       <c r="L276" s="32" t="n">
         <v>4035</v>
       </c>
-      <c r="M276" s="40" t="n">
+      <c r="M276" s="33" t="n">
         <v>4020</v>
       </c>
-      <c r="N276" s="40" t="n">
+      <c r="N276" s="33" t="n">
         <v>4005</v>
       </c>
-      <c r="O276" s="40" t="n">
+      <c r="O276" s="33" t="n">
         <v>3993.1</v>
       </c>
-      <c r="P276" s="41" t="n">
+      <c r="P276" s="34" t="n">
         <v>0.04</v>
       </c>
-      <c r="Q276" s="8" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="R276" s="8" t="n"/>
-      <c r="S276" s="8" t="n"/>
-      <c r="T276" s="40" t="n"/>
-      <c r="U276" s="47" t="n"/>
-      <c r="V276" s="43" t="inlineStr">
+      <c r="Q276" s="5" t="inlineStr">
+        <is>
+          <t>NO_FILL</t>
+        </is>
+      </c>
+      <c r="R276" s="5" t="n"/>
+      <c r="S276" s="5" t="n"/>
+      <c r="T276" s="33" t="n"/>
+      <c r="U276" s="35" t="n"/>
+      <c r="V276" s="36" t="inlineStr">
         <is>
           <t>1:1.3</t>
         </is>
       </c>
-      <c r="W276" s="48" t="n"/>
+      <c r="W276" s="37" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="31" t="inlineStr">
@@ -25601,33 +25782,33 @@
       <c r="L277" s="32" t="n">
         <v>4035</v>
       </c>
-      <c r="M277" s="40" t="n">
+      <c r="M277" s="33" t="n">
         <v>4020</v>
       </c>
-      <c r="N277" s="40" t="n">
+      <c r="N277" s="33" t="n">
         <v>4003.916666666667</v>
       </c>
-      <c r="O277" s="40" t="n">
+      <c r="O277" s="33" t="n">
         <v>3992.016666666666</v>
       </c>
-      <c r="P277" s="41" t="n">
+      <c r="P277" s="34" t="n">
         <v>0.04</v>
       </c>
-      <c r="Q277" s="8" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="R277" s="8" t="n"/>
-      <c r="S277" s="8" t="n"/>
-      <c r="T277" s="40" t="n"/>
-      <c r="U277" s="47" t="n"/>
-      <c r="V277" s="43" t="inlineStr">
+      <c r="Q277" s="5" t="inlineStr">
+        <is>
+          <t>NO_FILL</t>
+        </is>
+      </c>
+      <c r="R277" s="5" t="n"/>
+      <c r="S277" s="5" t="n"/>
+      <c r="T277" s="33" t="n"/>
+      <c r="U277" s="35" t="n"/>
+      <c r="V277" s="36" t="inlineStr">
         <is>
           <t>1:1.4</t>
         </is>
       </c>
-      <c r="W277" s="48" t="n"/>
+      <c r="W277" s="37" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="31" t="inlineStr">
@@ -25678,33 +25859,33 @@
       <c r="L278" s="32" t="n">
         <v>4035</v>
       </c>
-      <c r="M278" s="40" t="n">
+      <c r="M278" s="33" t="n">
         <v>4020</v>
       </c>
-      <c r="N278" s="40" t="n">
+      <c r="N278" s="33" t="n">
         <v>4002.833333333333</v>
       </c>
-      <c r="O278" s="40" t="n">
+      <c r="O278" s="33" t="n">
         <v>3990.933333333333</v>
       </c>
-      <c r="P278" s="41" t="n">
+      <c r="P278" s="34" t="n">
         <v>0.04</v>
       </c>
-      <c r="Q278" s="8" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="R278" s="8" t="n"/>
-      <c r="S278" s="8" t="n"/>
-      <c r="T278" s="40" t="n"/>
-      <c r="U278" s="47" t="n"/>
-      <c r="V278" s="43" t="inlineStr">
+      <c r="Q278" s="5" t="inlineStr">
+        <is>
+          <t>NO_FILL</t>
+        </is>
+      </c>
+      <c r="R278" s="5" t="n"/>
+      <c r="S278" s="5" t="n"/>
+      <c r="T278" s="33" t="n"/>
+      <c r="U278" s="35" t="n"/>
+      <c r="V278" s="36" t="inlineStr">
         <is>
           <t>1:1.4</t>
         </is>
       </c>
-      <c r="W278" s="48" t="n"/>
+      <c r="W278" s="37" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="31" t="inlineStr">
@@ -25755,33 +25936,33 @@
       <c r="L279" s="32" t="n">
         <v>4035</v>
       </c>
-      <c r="M279" s="40" t="n">
+      <c r="M279" s="33" t="n">
         <v>4020</v>
       </c>
-      <c r="N279" s="40" t="n">
+      <c r="N279" s="33" t="n">
         <v>4001.75</v>
       </c>
-      <c r="O279" s="40" t="n">
+      <c r="O279" s="33" t="n">
         <v>3989.85</v>
       </c>
-      <c r="P279" s="41" t="n">
+      <c r="P279" s="34" t="n">
         <v>0.04</v>
       </c>
-      <c r="Q279" s="8" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="R279" s="8" t="n"/>
-      <c r="S279" s="8" t="n"/>
-      <c r="T279" s="40" t="n"/>
-      <c r="U279" s="47" t="n"/>
-      <c r="V279" s="43" t="inlineStr">
+      <c r="Q279" s="5" t="inlineStr">
+        <is>
+          <t>NO_FILL</t>
+        </is>
+      </c>
+      <c r="R279" s="5" t="n"/>
+      <c r="S279" s="5" t="n"/>
+      <c r="T279" s="33" t="n"/>
+      <c r="U279" s="35" t="n"/>
+      <c r="V279" s="36" t="inlineStr">
         <is>
           <t>1:1.5</t>
         </is>
       </c>
-      <c r="W279" s="48" t="n"/>
+      <c r="W279" s="37" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="31" t="inlineStr">
@@ -25832,33 +26013,33 @@
       <c r="L280" s="32" t="n">
         <v>4035</v>
       </c>
-      <c r="M280" s="40" t="n">
+      <c r="M280" s="33" t="n">
         <v>4020</v>
       </c>
-      <c r="N280" s="40" t="n">
+      <c r="N280" s="33" t="n">
         <v>4000.666666666667</v>
       </c>
-      <c r="O280" s="40" t="n">
+      <c r="O280" s="33" t="n">
         <v>3988.766666666666</v>
       </c>
-      <c r="P280" s="41" t="n">
+      <c r="P280" s="34" t="n">
         <v>0.04</v>
       </c>
-      <c r="Q280" s="8" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="R280" s="8" t="n"/>
-      <c r="S280" s="8" t="n"/>
-      <c r="T280" s="40" t="n"/>
-      <c r="U280" s="47" t="n"/>
-      <c r="V280" s="43" t="inlineStr">
+      <c r="Q280" s="5" t="inlineStr">
+        <is>
+          <t>NO_FILL</t>
+        </is>
+      </c>
+      <c r="R280" s="5" t="n"/>
+      <c r="S280" s="5" t="n"/>
+      <c r="T280" s="33" t="n"/>
+      <c r="U280" s="35" t="n"/>
+      <c r="V280" s="36" t="inlineStr">
         <is>
           <t>1:1.6</t>
         </is>
       </c>
-      <c r="W280" s="48" t="n"/>
+      <c r="W280" s="37" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="31" t="inlineStr">
@@ -25909,33 +26090,33 @@
       <c r="L281" s="32" t="n">
         <v>4035</v>
       </c>
-      <c r="M281" s="40" t="n">
+      <c r="M281" s="33" t="n">
         <v>4020</v>
       </c>
-      <c r="N281" s="40" t="n">
+      <c r="N281" s="33" t="n">
         <v>3999.583333333333</v>
       </c>
-      <c r="O281" s="40" t="n">
+      <c r="O281" s="33" t="n">
         <v>3987.683333333333</v>
       </c>
-      <c r="P281" s="41" t="n">
+      <c r="P281" s="34" t="n">
         <v>0.04</v>
       </c>
-      <c r="Q281" s="8" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="R281" s="8" t="n"/>
-      <c r="S281" s="8" t="n"/>
-      <c r="T281" s="40" t="n"/>
-      <c r="U281" s="47" t="n"/>
-      <c r="V281" s="43" t="inlineStr">
+      <c r="Q281" s="5" t="inlineStr">
+        <is>
+          <t>NO_FILL</t>
+        </is>
+      </c>
+      <c r="R281" s="5" t="n"/>
+      <c r="S281" s="5" t="n"/>
+      <c r="T281" s="33" t="n"/>
+      <c r="U281" s="35" t="n"/>
+      <c r="V281" s="36" t="inlineStr">
         <is>
           <t>1:1.7</t>
         </is>
       </c>
-      <c r="W281" s="48" t="n"/>
+      <c r="W281" s="37" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="31" t="inlineStr">
@@ -25986,36 +26167,1765 @@
       <c r="L282" s="32" t="n">
         <v>4035</v>
       </c>
-      <c r="M282" s="40" t="n">
+      <c r="M282" s="33" t="n">
         <v>4020</v>
       </c>
-      <c r="N282" s="40" t="n">
+      <c r="N282" s="33" t="n">
         <v>3998.5</v>
       </c>
-      <c r="O282" s="40" t="n">
+      <c r="O282" s="33" t="n">
         <v>3986.6</v>
       </c>
-      <c r="P282" s="41" t="n">
+      <c r="P282" s="34" t="n">
         <v>0.04</v>
       </c>
-      <c r="Q282" s="8" t="inlineStr">
+      <c r="Q282" s="5" t="inlineStr">
+        <is>
+          <t>NO_FILL</t>
+        </is>
+      </c>
+      <c r="R282" s="5" t="n"/>
+      <c r="S282" s="5" t="n"/>
+      <c r="T282" s="33" t="n"/>
+      <c r="U282" s="35" t="n"/>
+      <c r="V282" s="36" t="inlineStr">
+        <is>
+          <t>1:1.8</t>
+        </is>
+      </c>
+      <c r="W282" s="37" t="n"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26#01.1</t>
+        </is>
+      </c>
+      <c r="B283" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C283" s="31" t="inlineStr">
+        <is>
+          <t>11:04 AM</t>
+        </is>
+      </c>
+      <c r="D283" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26 07:04</t>
+        </is>
+      </c>
+      <c r="E283" s="31" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F283" s="31" t="inlineStr">
+        <is>
+          <t>TICK</t>
+        </is>
+      </c>
+      <c r="G283" s="32" t="n">
+        <v>4010</v>
+      </c>
+      <c r="H283" s="32" t="n">
+        <v>4012</v>
+      </c>
+      <c r="I283" s="32" t="n">
+        <v>4017.5</v>
+      </c>
+      <c r="J283" s="32" t="n">
+        <v>4005</v>
+      </c>
+      <c r="K283" s="32" t="n">
+        <v>3995</v>
+      </c>
+      <c r="L283" s="32" t="n">
+        <v>3978</v>
+      </c>
+      <c r="M283" s="38" t="n">
+        <v>3995</v>
+      </c>
+      <c r="N283" s="38" t="n">
+        <v>4010.07</v>
+      </c>
+      <c r="O283" s="38" t="n">
+        <v>4022.75</v>
+      </c>
+      <c r="P283" s="17" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Q283" s="6" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="R283" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-26 08:07</t>
+        </is>
+      </c>
+      <c r="S283" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-26 09:36</t>
+        </is>
+      </c>
+      <c r="T283" s="38" t="n">
+        <v>4022.75</v>
+      </c>
+      <c r="U283" s="15" t="n">
+        <v>-38.03999999999951</v>
+      </c>
+      <c r="V283" s="13" t="inlineStr">
+        <is>
+          <t>1:1.2</t>
+        </is>
+      </c>
+      <c r="W283" s="14" t="inlineStr">
+        <is>
+          <t>-1.0R</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26#01.2</t>
+        </is>
+      </c>
+      <c r="B284" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C284" s="31" t="inlineStr">
+        <is>
+          <t>11:04 AM</t>
+        </is>
+      </c>
+      <c r="D284" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26 07:04</t>
+        </is>
+      </c>
+      <c r="E284" s="31" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F284" s="31" t="inlineStr">
+        <is>
+          <t>TICK</t>
+        </is>
+      </c>
+      <c r="G284" s="32" t="n">
+        <v>4010</v>
+      </c>
+      <c r="H284" s="32" t="n">
+        <v>4012</v>
+      </c>
+      <c r="I284" s="32" t="n">
+        <v>4017.5</v>
+      </c>
+      <c r="J284" s="32" t="n">
+        <v>4005</v>
+      </c>
+      <c r="K284" s="32" t="n">
+        <v>3995</v>
+      </c>
+      <c r="L284" s="32" t="n">
+        <v>3978</v>
+      </c>
+      <c r="M284" s="38" t="n">
+        <v>3995</v>
+      </c>
+      <c r="N284" s="38" t="n">
+        <v>4013.61</v>
+      </c>
+      <c r="O284" s="38" t="n">
+        <v>4023.916666666667</v>
+      </c>
+      <c r="P284" s="17" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Q284" s="6" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="R284" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-26 08:20</t>
+        </is>
+      </c>
+      <c r="S284" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-26 09:36</t>
+        </is>
+      </c>
+      <c r="T284" s="38" t="n">
+        <v>4023.92</v>
+      </c>
+      <c r="U284" s="15" t="n">
+        <v>-30.92999999999984</v>
+      </c>
+      <c r="V284" s="13" t="inlineStr">
+        <is>
+          <t>1:1.3</t>
+        </is>
+      </c>
+      <c r="W284" s="14" t="inlineStr">
+        <is>
+          <t>-1.0R</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26#01.3</t>
+        </is>
+      </c>
+      <c r="B285" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C285" s="31" t="inlineStr">
+        <is>
+          <t>11:04 AM</t>
+        </is>
+      </c>
+      <c r="D285" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26 07:04</t>
+        </is>
+      </c>
+      <c r="E285" s="31" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F285" s="31" t="inlineStr">
+        <is>
+          <t>TICK</t>
+        </is>
+      </c>
+      <c r="G285" s="32" t="n">
+        <v>4010</v>
+      </c>
+      <c r="H285" s="32" t="n">
+        <v>4012</v>
+      </c>
+      <c r="I285" s="32" t="n">
+        <v>4017.5</v>
+      </c>
+      <c r="J285" s="32" t="n">
+        <v>4005</v>
+      </c>
+      <c r="K285" s="32" t="n">
+        <v>3995</v>
+      </c>
+      <c r="L285" s="32" t="n">
+        <v>3978</v>
+      </c>
+      <c r="M285" s="38" t="n">
+        <v>3995</v>
+      </c>
+      <c r="N285" s="38" t="n">
+        <v>4013.61</v>
+      </c>
+      <c r="O285" s="38" t="n">
+        <v>4025.083333333333</v>
+      </c>
+      <c r="P285" s="17" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Q285" s="6" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="R285" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-26 08:20</t>
+        </is>
+      </c>
+      <c r="S285" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-26 09:36</t>
+        </is>
+      </c>
+      <c r="T285" s="38" t="n">
+        <v>4025.08</v>
+      </c>
+      <c r="U285" s="15" t="n">
+        <v>-34.4099999999994</v>
+      </c>
+      <c r="V285" s="13" t="inlineStr">
+        <is>
+          <t>1:1.4</t>
+        </is>
+      </c>
+      <c r="W285" s="14" t="inlineStr">
+        <is>
+          <t>-1.0R</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26#01.4</t>
+        </is>
+      </c>
+      <c r="B286" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C286" s="31" t="inlineStr">
+        <is>
+          <t>11:04 AM</t>
+        </is>
+      </c>
+      <c r="D286" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26 07:04</t>
+        </is>
+      </c>
+      <c r="E286" s="31" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F286" s="31" t="inlineStr">
+        <is>
+          <t>TICK</t>
+        </is>
+      </c>
+      <c r="G286" s="32" t="n">
+        <v>4010</v>
+      </c>
+      <c r="H286" s="32" t="n">
+        <v>4012</v>
+      </c>
+      <c r="I286" s="32" t="n">
+        <v>4017.5</v>
+      </c>
+      <c r="J286" s="32" t="n">
+        <v>4005</v>
+      </c>
+      <c r="K286" s="32" t="n">
+        <v>3995</v>
+      </c>
+      <c r="L286" s="32" t="n">
+        <v>3978</v>
+      </c>
+      <c r="M286" s="38" t="n">
+        <v>3995</v>
+      </c>
+      <c r="N286" s="38" t="n">
+        <v>4013.61</v>
+      </c>
+      <c r="O286" s="38" t="n">
+        <v>4026.25</v>
+      </c>
+      <c r="P286" s="17" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Q286" s="6" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="R286" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-26 08:20</t>
+        </is>
+      </c>
+      <c r="S286" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-26 09:44</t>
+        </is>
+      </c>
+      <c r="T286" s="38" t="n">
+        <v>4026.25</v>
+      </c>
+      <c r="U286" s="15" t="n">
+        <v>-37.91999999999962</v>
+      </c>
+      <c r="V286" s="13" t="inlineStr">
+        <is>
+          <t>1:1.5</t>
+        </is>
+      </c>
+      <c r="W286" s="14" t="inlineStr">
+        <is>
+          <t>-1.0R</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26#01.5</t>
+        </is>
+      </c>
+      <c r="B287" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C287" s="31" t="inlineStr">
+        <is>
+          <t>11:04 AM</t>
+        </is>
+      </c>
+      <c r="D287" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26 07:04</t>
+        </is>
+      </c>
+      <c r="E287" s="31" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F287" s="31" t="inlineStr">
+        <is>
+          <t>TICK</t>
+        </is>
+      </c>
+      <c r="G287" s="32" t="n">
+        <v>4010</v>
+      </c>
+      <c r="H287" s="32" t="n">
+        <v>4012</v>
+      </c>
+      <c r="I287" s="32" t="n">
+        <v>4017.5</v>
+      </c>
+      <c r="J287" s="32" t="n">
+        <v>4005</v>
+      </c>
+      <c r="K287" s="32" t="n">
+        <v>3995</v>
+      </c>
+      <c r="L287" s="32" t="n">
+        <v>3978</v>
+      </c>
+      <c r="M287" s="38" t="n">
+        <v>3995</v>
+      </c>
+      <c r="N287" s="38" t="n">
+        <v>4014.69</v>
+      </c>
+      <c r="O287" s="38" t="n">
+        <v>4027.416666666667</v>
+      </c>
+      <c r="P287" s="17" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Q287" s="6" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="R287" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-26 08:26</t>
+        </is>
+      </c>
+      <c r="S287" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-26 09:46</t>
+        </is>
+      </c>
+      <c r="T287" s="38" t="n">
+        <v>4027.42</v>
+      </c>
+      <c r="U287" s="15" t="n">
+        <v>-38.19000000000005</v>
+      </c>
+      <c r="V287" s="13" t="inlineStr">
+        <is>
+          <t>1:1.5</t>
+        </is>
+      </c>
+      <c r="W287" s="14" t="inlineStr">
+        <is>
+          <t>-1.0R</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26#01.6</t>
+        </is>
+      </c>
+      <c r="B288" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C288" s="31" t="inlineStr">
+        <is>
+          <t>11:04 AM</t>
+        </is>
+      </c>
+      <c r="D288" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26 07:04</t>
+        </is>
+      </c>
+      <c r="E288" s="31" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F288" s="31" t="inlineStr">
+        <is>
+          <t>TICK</t>
+        </is>
+      </c>
+      <c r="G288" s="32" t="n">
+        <v>4010</v>
+      </c>
+      <c r="H288" s="32" t="n">
+        <v>4012</v>
+      </c>
+      <c r="I288" s="32" t="n">
+        <v>4017.5</v>
+      </c>
+      <c r="J288" s="32" t="n">
+        <v>4005</v>
+      </c>
+      <c r="K288" s="32" t="n">
+        <v>3995</v>
+      </c>
+      <c r="L288" s="32" t="n">
+        <v>3978</v>
+      </c>
+      <c r="M288" s="38" t="n">
+        <v>3995</v>
+      </c>
+      <c r="N288" s="38" t="n">
+        <v>4015.83</v>
+      </c>
+      <c r="O288" s="38" t="n">
+        <v>4028.583333333333</v>
+      </c>
+      <c r="P288" s="17" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Q288" s="6" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="R288" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-26 08:26</t>
+        </is>
+      </c>
+      <c r="S288" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-26 09:55</t>
+        </is>
+      </c>
+      <c r="T288" s="38" t="n">
+        <v>4028.58</v>
+      </c>
+      <c r="U288" s="15" t="n">
+        <v>-38.25</v>
+      </c>
+      <c r="V288" s="13" t="inlineStr">
+        <is>
+          <t>1:1.6</t>
+        </is>
+      </c>
+      <c r="W288" s="14" t="inlineStr">
+        <is>
+          <t>-1.0R</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26#01.7</t>
+        </is>
+      </c>
+      <c r="B289" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C289" s="31" t="inlineStr">
+        <is>
+          <t>11:04 AM</t>
+        </is>
+      </c>
+      <c r="D289" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26 07:04</t>
+        </is>
+      </c>
+      <c r="E289" s="31" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F289" s="31" t="inlineStr">
+        <is>
+          <t>TICK</t>
+        </is>
+      </c>
+      <c r="G289" s="32" t="n">
+        <v>4010</v>
+      </c>
+      <c r="H289" s="32" t="n">
+        <v>4012</v>
+      </c>
+      <c r="I289" s="32" t="n">
+        <v>4017.5</v>
+      </c>
+      <c r="J289" s="32" t="n">
+        <v>4005</v>
+      </c>
+      <c r="K289" s="32" t="n">
+        <v>3995</v>
+      </c>
+      <c r="L289" s="32" t="n">
+        <v>3978</v>
+      </c>
+      <c r="M289" s="38" t="n">
+        <v>3995</v>
+      </c>
+      <c r="N289" s="38" t="n">
+        <v>4017.08</v>
+      </c>
+      <c r="O289" s="38" t="n">
+        <v>4029.75</v>
+      </c>
+      <c r="P289" s="17" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Q289" s="6" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="R289" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-26 08:28</t>
+        </is>
+      </c>
+      <c r="S289" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-26 09:57</t>
+        </is>
+      </c>
+      <c r="T289" s="38" t="n">
+        <v>4029.75</v>
+      </c>
+      <c r="U289" s="15" t="n">
+        <v>-38.01000000000022</v>
+      </c>
+      <c r="V289" s="13" t="inlineStr">
+        <is>
+          <t>1:1.7</t>
+        </is>
+      </c>
+      <c r="W289" s="14" t="inlineStr">
+        <is>
+          <t>-1.0R</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26#02.1</t>
+        </is>
+      </c>
+      <c r="B290" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C290" s="31" t="inlineStr">
+        <is>
+          <t>2:04 PM</t>
+        </is>
+      </c>
+      <c r="D290" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26 10:04</t>
+        </is>
+      </c>
+      <c r="E290" s="31" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F290" s="31" t="inlineStr">
+        <is>
+          <t>TICK</t>
+        </is>
+      </c>
+      <c r="G290" s="32" t="n">
+        <v>4008</v>
+      </c>
+      <c r="H290" s="32" t="n">
+        <v>4010</v>
+      </c>
+      <c r="I290" s="32" t="n">
+        <v>4003</v>
+      </c>
+      <c r="J290" s="32" t="n">
+        <v>4015</v>
+      </c>
+      <c r="K290" s="32" t="n">
+        <v>4025</v>
+      </c>
+      <c r="L290" s="32" t="n">
+        <v>4040</v>
+      </c>
+      <c r="M290" s="40" t="n">
+        <v>4025</v>
+      </c>
+      <c r="N290" s="40" t="n">
+        <v>4010</v>
+      </c>
+      <c r="O290" s="40" t="n">
+        <v>3998.1</v>
+      </c>
+      <c r="P290" s="41" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Q290" s="8" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="R282" s="8" t="n"/>
-      <c r="S282" s="8" t="n"/>
-      <c r="T282" s="40" t="n"/>
-      <c r="U282" s="47" t="n"/>
-      <c r="V282" s="43" t="inlineStr">
+      <c r="R290" s="8" t="n"/>
+      <c r="S290" s="8" t="n"/>
+      <c r="T290" s="40" t="n"/>
+      <c r="U290" s="47" t="n"/>
+      <c r="V290" s="43" t="inlineStr">
+        <is>
+          <t>1:1.3</t>
+        </is>
+      </c>
+      <c r="W290" s="48" t="n"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26#02.2</t>
+        </is>
+      </c>
+      <c r="B291" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C291" s="31" t="inlineStr">
+        <is>
+          <t>2:04 PM</t>
+        </is>
+      </c>
+      <c r="D291" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26 10:04</t>
+        </is>
+      </c>
+      <c r="E291" s="31" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F291" s="31" t="inlineStr">
+        <is>
+          <t>TICK</t>
+        </is>
+      </c>
+      <c r="G291" s="32" t="n">
+        <v>4008</v>
+      </c>
+      <c r="H291" s="32" t="n">
+        <v>4010</v>
+      </c>
+      <c r="I291" s="32" t="n">
+        <v>4003</v>
+      </c>
+      <c r="J291" s="32" t="n">
+        <v>4015</v>
+      </c>
+      <c r="K291" s="32" t="n">
+        <v>4025</v>
+      </c>
+      <c r="L291" s="32" t="n">
+        <v>4040</v>
+      </c>
+      <c r="M291" s="40" t="n">
+        <v>4025</v>
+      </c>
+      <c r="N291" s="40" t="n">
+        <v>4008.916666666667</v>
+      </c>
+      <c r="O291" s="40" t="n">
+        <v>3997.016666666666</v>
+      </c>
+      <c r="P291" s="41" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Q291" s="8" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="R291" s="8" t="n"/>
+      <c r="S291" s="8" t="n"/>
+      <c r="T291" s="40" t="n"/>
+      <c r="U291" s="47" t="n"/>
+      <c r="V291" s="43" t="inlineStr">
+        <is>
+          <t>1:1.4</t>
+        </is>
+      </c>
+      <c r="W291" s="48" t="n"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26#02.3</t>
+        </is>
+      </c>
+      <c r="B292" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C292" s="31" t="inlineStr">
+        <is>
+          <t>2:04 PM</t>
+        </is>
+      </c>
+      <c r="D292" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26 10:04</t>
+        </is>
+      </c>
+      <c r="E292" s="31" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F292" s="31" t="inlineStr">
+        <is>
+          <t>TICK</t>
+        </is>
+      </c>
+      <c r="G292" s="32" t="n">
+        <v>4008</v>
+      </c>
+      <c r="H292" s="32" t="n">
+        <v>4010</v>
+      </c>
+      <c r="I292" s="32" t="n">
+        <v>4003</v>
+      </c>
+      <c r="J292" s="32" t="n">
+        <v>4015</v>
+      </c>
+      <c r="K292" s="32" t="n">
+        <v>4025</v>
+      </c>
+      <c r="L292" s="32" t="n">
+        <v>4040</v>
+      </c>
+      <c r="M292" s="40" t="n">
+        <v>4025</v>
+      </c>
+      <c r="N292" s="40" t="n">
+        <v>4007.833333333333</v>
+      </c>
+      <c r="O292" s="40" t="n">
+        <v>3995.933333333333</v>
+      </c>
+      <c r="P292" s="41" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Q292" s="8" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="R292" s="8" t="n"/>
+      <c r="S292" s="8" t="n"/>
+      <c r="T292" s="40" t="n"/>
+      <c r="U292" s="47" t="n"/>
+      <c r="V292" s="43" t="inlineStr">
+        <is>
+          <t>1:1.4</t>
+        </is>
+      </c>
+      <c r="W292" s="48" t="n"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26#02.4</t>
+        </is>
+      </c>
+      <c r="B293" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C293" s="31" t="inlineStr">
+        <is>
+          <t>2:04 PM</t>
+        </is>
+      </c>
+      <c r="D293" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26 10:04</t>
+        </is>
+      </c>
+      <c r="E293" s="31" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F293" s="31" t="inlineStr">
+        <is>
+          <t>TICK</t>
+        </is>
+      </c>
+      <c r="G293" s="32" t="n">
+        <v>4008</v>
+      </c>
+      <c r="H293" s="32" t="n">
+        <v>4010</v>
+      </c>
+      <c r="I293" s="32" t="n">
+        <v>4003</v>
+      </c>
+      <c r="J293" s="32" t="n">
+        <v>4015</v>
+      </c>
+      <c r="K293" s="32" t="n">
+        <v>4025</v>
+      </c>
+      <c r="L293" s="32" t="n">
+        <v>4040</v>
+      </c>
+      <c r="M293" s="40" t="n">
+        <v>4025</v>
+      </c>
+      <c r="N293" s="40" t="n">
+        <v>4006.75</v>
+      </c>
+      <c r="O293" s="40" t="n">
+        <v>3994.85</v>
+      </c>
+      <c r="P293" s="41" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Q293" s="8" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="R293" s="8" t="n"/>
+      <c r="S293" s="8" t="n"/>
+      <c r="T293" s="40" t="n"/>
+      <c r="U293" s="47" t="n"/>
+      <c r="V293" s="43" t="inlineStr">
+        <is>
+          <t>1:1.5</t>
+        </is>
+      </c>
+      <c r="W293" s="48" t="n"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26#02.5</t>
+        </is>
+      </c>
+      <c r="B294" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C294" s="31" t="inlineStr">
+        <is>
+          <t>2:04 PM</t>
+        </is>
+      </c>
+      <c r="D294" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26 10:04</t>
+        </is>
+      </c>
+      <c r="E294" s="31" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F294" s="31" t="inlineStr">
+        <is>
+          <t>TICK</t>
+        </is>
+      </c>
+      <c r="G294" s="32" t="n">
+        <v>4008</v>
+      </c>
+      <c r="H294" s="32" t="n">
+        <v>4010</v>
+      </c>
+      <c r="I294" s="32" t="n">
+        <v>4003</v>
+      </c>
+      <c r="J294" s="32" t="n">
+        <v>4015</v>
+      </c>
+      <c r="K294" s="32" t="n">
+        <v>4025</v>
+      </c>
+      <c r="L294" s="32" t="n">
+        <v>4040</v>
+      </c>
+      <c r="M294" s="40" t="n">
+        <v>4025</v>
+      </c>
+      <c r="N294" s="40" t="n">
+        <v>4005.666666666667</v>
+      </c>
+      <c r="O294" s="40" t="n">
+        <v>3993.766666666666</v>
+      </c>
+      <c r="P294" s="41" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Q294" s="8" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="R294" s="8" t="n"/>
+      <c r="S294" s="8" t="n"/>
+      <c r="T294" s="40" t="n"/>
+      <c r="U294" s="47" t="n"/>
+      <c r="V294" s="43" t="inlineStr">
+        <is>
+          <t>1:1.6</t>
+        </is>
+      </c>
+      <c r="W294" s="48" t="n"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26#02.6</t>
+        </is>
+      </c>
+      <c r="B295" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C295" s="31" t="inlineStr">
+        <is>
+          <t>2:04 PM</t>
+        </is>
+      </c>
+      <c r="D295" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26 10:04</t>
+        </is>
+      </c>
+      <c r="E295" s="31" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F295" s="31" t="inlineStr">
+        <is>
+          <t>TICK</t>
+        </is>
+      </c>
+      <c r="G295" s="32" t="n">
+        <v>4008</v>
+      </c>
+      <c r="H295" s="32" t="n">
+        <v>4010</v>
+      </c>
+      <c r="I295" s="32" t="n">
+        <v>4003</v>
+      </c>
+      <c r="J295" s="32" t="n">
+        <v>4015</v>
+      </c>
+      <c r="K295" s="32" t="n">
+        <v>4025</v>
+      </c>
+      <c r="L295" s="32" t="n">
+        <v>4040</v>
+      </c>
+      <c r="M295" s="40" t="n">
+        <v>4025</v>
+      </c>
+      <c r="N295" s="40" t="n">
+        <v>4004.583333333333</v>
+      </c>
+      <c r="O295" s="40" t="n">
+        <v>3992.683333333333</v>
+      </c>
+      <c r="P295" s="41" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Q295" s="8" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="R295" s="8" t="n"/>
+      <c r="S295" s="8" t="n"/>
+      <c r="T295" s="40" t="n"/>
+      <c r="U295" s="47" t="n"/>
+      <c r="V295" s="43" t="inlineStr">
+        <is>
+          <t>1:1.7</t>
+        </is>
+      </c>
+      <c r="W295" s="48" t="n"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26#02.7</t>
+        </is>
+      </c>
+      <c r="B296" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C296" s="31" t="inlineStr">
+        <is>
+          <t>2:04 PM</t>
+        </is>
+      </c>
+      <c r="D296" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26 10:04</t>
+        </is>
+      </c>
+      <c r="E296" s="31" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F296" s="31" t="inlineStr">
+        <is>
+          <t>TICK</t>
+        </is>
+      </c>
+      <c r="G296" s="32" t="n">
+        <v>4008</v>
+      </c>
+      <c r="H296" s="32" t="n">
+        <v>4010</v>
+      </c>
+      <c r="I296" s="32" t="n">
+        <v>4003</v>
+      </c>
+      <c r="J296" s="32" t="n">
+        <v>4015</v>
+      </c>
+      <c r="K296" s="32" t="n">
+        <v>4025</v>
+      </c>
+      <c r="L296" s="32" t="n">
+        <v>4040</v>
+      </c>
+      <c r="M296" s="40" t="n">
+        <v>4025</v>
+      </c>
+      <c r="N296" s="40" t="n">
+        <v>4003.5</v>
+      </c>
+      <c r="O296" s="40" t="n">
+        <v>3991.6</v>
+      </c>
+      <c r="P296" s="41" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Q296" s="8" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="R296" s="8" t="n"/>
+      <c r="S296" s="8" t="n"/>
+      <c r="T296" s="40" t="n"/>
+      <c r="U296" s="47" t="n"/>
+      <c r="V296" s="43" t="inlineStr">
         <is>
           <t>1:1.8</t>
         </is>
       </c>
-      <c r="W282" s="48" t="n"/>
+      <c r="W296" s="48" t="n"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26#03.1</t>
+        </is>
+      </c>
+      <c r="B297" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C297" s="31" t="inlineStr">
+        <is>
+          <t>2:40 PM</t>
+        </is>
+      </c>
+      <c r="D297" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26 10:40</t>
+        </is>
+      </c>
+      <c r="E297" s="31" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F297" s="31" t="inlineStr">
+        <is>
+          <t>TICK</t>
+        </is>
+      </c>
+      <c r="G297" s="32" t="n">
+        <v>4023</v>
+      </c>
+      <c r="H297" s="32" t="n">
+        <v>4025</v>
+      </c>
+      <c r="I297" s="32" t="n">
+        <v>4018</v>
+      </c>
+      <c r="J297" s="32" t="n">
+        <v>4030</v>
+      </c>
+      <c r="K297" s="32" t="n">
+        <v>4040</v>
+      </c>
+      <c r="L297" s="32" t="n">
+        <v>4060</v>
+      </c>
+      <c r="M297" s="40" t="n">
+        <v>4040</v>
+      </c>
+      <c r="N297" s="40" t="n">
+        <v>4025</v>
+      </c>
+      <c r="O297" s="40" t="n">
+        <v>4013.1</v>
+      </c>
+      <c r="P297" s="41" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Q297" s="8" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="R297" s="8" t="n"/>
+      <c r="S297" s="8" t="n"/>
+      <c r="T297" s="40" t="n"/>
+      <c r="U297" s="47" t="n"/>
+      <c r="V297" s="43" t="inlineStr">
+        <is>
+          <t>1:1.3</t>
+        </is>
+      </c>
+      <c r="W297" s="48" t="n"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26#03.2</t>
+        </is>
+      </c>
+      <c r="B298" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C298" s="31" t="inlineStr">
+        <is>
+          <t>2:40 PM</t>
+        </is>
+      </c>
+      <c r="D298" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26 10:40</t>
+        </is>
+      </c>
+      <c r="E298" s="31" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F298" s="31" t="inlineStr">
+        <is>
+          <t>TICK</t>
+        </is>
+      </c>
+      <c r="G298" s="32" t="n">
+        <v>4023</v>
+      </c>
+      <c r="H298" s="32" t="n">
+        <v>4025</v>
+      </c>
+      <c r="I298" s="32" t="n">
+        <v>4018</v>
+      </c>
+      <c r="J298" s="32" t="n">
+        <v>4030</v>
+      </c>
+      <c r="K298" s="32" t="n">
+        <v>4040</v>
+      </c>
+      <c r="L298" s="32" t="n">
+        <v>4060</v>
+      </c>
+      <c r="M298" s="40" t="n">
+        <v>4040</v>
+      </c>
+      <c r="N298" s="40" t="n">
+        <v>4023.916666666667</v>
+      </c>
+      <c r="O298" s="40" t="n">
+        <v>4012.016666666666</v>
+      </c>
+      <c r="P298" s="41" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Q298" s="8" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="R298" s="8" t="n"/>
+      <c r="S298" s="8" t="n"/>
+      <c r="T298" s="40" t="n"/>
+      <c r="U298" s="47" t="n"/>
+      <c r="V298" s="43" t="inlineStr">
+        <is>
+          <t>1:1.4</t>
+        </is>
+      </c>
+      <c r="W298" s="48" t="n"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26#03.3</t>
+        </is>
+      </c>
+      <c r="B299" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C299" s="31" t="inlineStr">
+        <is>
+          <t>2:40 PM</t>
+        </is>
+      </c>
+      <c r="D299" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26 10:40</t>
+        </is>
+      </c>
+      <c r="E299" s="31" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F299" s="31" t="inlineStr">
+        <is>
+          <t>TICK</t>
+        </is>
+      </c>
+      <c r="G299" s="32" t="n">
+        <v>4023</v>
+      </c>
+      <c r="H299" s="32" t="n">
+        <v>4025</v>
+      </c>
+      <c r="I299" s="32" t="n">
+        <v>4018</v>
+      </c>
+      <c r="J299" s="32" t="n">
+        <v>4030</v>
+      </c>
+      <c r="K299" s="32" t="n">
+        <v>4040</v>
+      </c>
+      <c r="L299" s="32" t="n">
+        <v>4060</v>
+      </c>
+      <c r="M299" s="40" t="n">
+        <v>4040</v>
+      </c>
+      <c r="N299" s="40" t="n">
+        <v>4022.833333333333</v>
+      </c>
+      <c r="O299" s="40" t="n">
+        <v>4010.933333333333</v>
+      </c>
+      <c r="P299" s="41" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Q299" s="8" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="R299" s="8" t="n"/>
+      <c r="S299" s="8" t="n"/>
+      <c r="T299" s="40" t="n"/>
+      <c r="U299" s="47" t="n"/>
+      <c r="V299" s="43" t="inlineStr">
+        <is>
+          <t>1:1.4</t>
+        </is>
+      </c>
+      <c r="W299" s="48" t="n"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26#03.4</t>
+        </is>
+      </c>
+      <c r="B300" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C300" s="31" t="inlineStr">
+        <is>
+          <t>2:40 PM</t>
+        </is>
+      </c>
+      <c r="D300" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26 10:40</t>
+        </is>
+      </c>
+      <c r="E300" s="31" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F300" s="31" t="inlineStr">
+        <is>
+          <t>TICK</t>
+        </is>
+      </c>
+      <c r="G300" s="32" t="n">
+        <v>4023</v>
+      </c>
+      <c r="H300" s="32" t="n">
+        <v>4025</v>
+      </c>
+      <c r="I300" s="32" t="n">
+        <v>4018</v>
+      </c>
+      <c r="J300" s="32" t="n">
+        <v>4030</v>
+      </c>
+      <c r="K300" s="32" t="n">
+        <v>4040</v>
+      </c>
+      <c r="L300" s="32" t="n">
+        <v>4060</v>
+      </c>
+      <c r="M300" s="40" t="n">
+        <v>4040</v>
+      </c>
+      <c r="N300" s="40" t="n">
+        <v>4021.75</v>
+      </c>
+      <c r="O300" s="40" t="n">
+        <v>4009.85</v>
+      </c>
+      <c r="P300" s="41" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Q300" s="8" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="R300" s="8" t="n"/>
+      <c r="S300" s="8" t="n"/>
+      <c r="T300" s="40" t="n"/>
+      <c r="U300" s="47" t="n"/>
+      <c r="V300" s="43" t="inlineStr">
+        <is>
+          <t>1:1.5</t>
+        </is>
+      </c>
+      <c r="W300" s="48" t="n"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26#03.5</t>
+        </is>
+      </c>
+      <c r="B301" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C301" s="31" t="inlineStr">
+        <is>
+          <t>2:40 PM</t>
+        </is>
+      </c>
+      <c r="D301" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26 10:40</t>
+        </is>
+      </c>
+      <c r="E301" s="31" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F301" s="31" t="inlineStr">
+        <is>
+          <t>TICK</t>
+        </is>
+      </c>
+      <c r="G301" s="32" t="n">
+        <v>4023</v>
+      </c>
+      <c r="H301" s="32" t="n">
+        <v>4025</v>
+      </c>
+      <c r="I301" s="32" t="n">
+        <v>4018</v>
+      </c>
+      <c r="J301" s="32" t="n">
+        <v>4030</v>
+      </c>
+      <c r="K301" s="32" t="n">
+        <v>4040</v>
+      </c>
+      <c r="L301" s="32" t="n">
+        <v>4060</v>
+      </c>
+      <c r="M301" s="40" t="n">
+        <v>4040</v>
+      </c>
+      <c r="N301" s="40" t="n">
+        <v>4020.666666666667</v>
+      </c>
+      <c r="O301" s="40" t="n">
+        <v>4008.766666666666</v>
+      </c>
+      <c r="P301" s="41" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Q301" s="8" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="R301" s="8" t="n"/>
+      <c r="S301" s="8" t="n"/>
+      <c r="T301" s="40" t="n"/>
+      <c r="U301" s="47" t="n"/>
+      <c r="V301" s="43" t="inlineStr">
+        <is>
+          <t>1:1.6</t>
+        </is>
+      </c>
+      <c r="W301" s="48" t="n"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26#03.6</t>
+        </is>
+      </c>
+      <c r="B302" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C302" s="31" t="inlineStr">
+        <is>
+          <t>2:40 PM</t>
+        </is>
+      </c>
+      <c r="D302" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26 10:40</t>
+        </is>
+      </c>
+      <c r="E302" s="31" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F302" s="31" t="inlineStr">
+        <is>
+          <t>TICK</t>
+        </is>
+      </c>
+      <c r="G302" s="32" t="n">
+        <v>4023</v>
+      </c>
+      <c r="H302" s="32" t="n">
+        <v>4025</v>
+      </c>
+      <c r="I302" s="32" t="n">
+        <v>4018</v>
+      </c>
+      <c r="J302" s="32" t="n">
+        <v>4030</v>
+      </c>
+      <c r="K302" s="32" t="n">
+        <v>4040</v>
+      </c>
+      <c r="L302" s="32" t="n">
+        <v>4060</v>
+      </c>
+      <c r="M302" s="40" t="n">
+        <v>4040</v>
+      </c>
+      <c r="N302" s="40" t="n">
+        <v>4019.583333333333</v>
+      </c>
+      <c r="O302" s="40" t="n">
+        <v>4007.683333333333</v>
+      </c>
+      <c r="P302" s="41" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Q302" s="8" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="R302" s="8" t="n"/>
+      <c r="S302" s="8" t="n"/>
+      <c r="T302" s="40" t="n"/>
+      <c r="U302" s="47" t="n"/>
+      <c r="V302" s="43" t="inlineStr">
+        <is>
+          <t>1:1.7</t>
+        </is>
+      </c>
+      <c r="W302" s="48" t="n"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26#03.7</t>
+        </is>
+      </c>
+      <c r="B303" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C303" s="31" t="inlineStr">
+        <is>
+          <t>2:40 PM</t>
+        </is>
+      </c>
+      <c r="D303" s="31" t="inlineStr">
+        <is>
+          <t>2026-06-26 10:40</t>
+        </is>
+      </c>
+      <c r="E303" s="31" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F303" s="31" t="inlineStr">
+        <is>
+          <t>TICK</t>
+        </is>
+      </c>
+      <c r="G303" s="32" t="n">
+        <v>4023</v>
+      </c>
+      <c r="H303" s="32" t="n">
+        <v>4025</v>
+      </c>
+      <c r="I303" s="32" t="n">
+        <v>4018</v>
+      </c>
+      <c r="J303" s="32" t="n">
+        <v>4030</v>
+      </c>
+      <c r="K303" s="32" t="n">
+        <v>4040</v>
+      </c>
+      <c r="L303" s="32" t="n">
+        <v>4060</v>
+      </c>
+      <c r="M303" s="40" t="n">
+        <v>4040</v>
+      </c>
+      <c r="N303" s="40" t="n">
+        <v>4018.5</v>
+      </c>
+      <c r="O303" s="40" t="n">
+        <v>4006.6</v>
+      </c>
+      <c r="P303" s="41" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Q303" s="8" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="R303" s="8" t="n"/>
+      <c r="S303" s="8" t="n"/>
+      <c r="T303" s="40" t="n"/>
+      <c r="U303" s="47" t="n"/>
+      <c r="V303" s="43" t="inlineStr">
+        <is>
+          <t>1:1.8</t>
+        </is>
+      </c>
+      <c r="W303" s="48" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:W282"/>
+  <autoFilter ref="A2:W303"/>
   <mergeCells count="3">
     <mergeCell ref="G1:L1"/>
     <mergeCell ref="A1:F1"/>
